--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП КОМПЛЕКС ЗА ДЕТСКО ХРАНЕНЕ/ОП КОМПЛЕКС ЗА ДЕТСКО ХРАНЕНЕ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП КОМПЛЕКС ЗА ДЕТСКО ХРАНЕНЕ/ОП КОМПЛЕКС ЗА ДЕТСКО ХРАНЕНЕ.xlsx
@@ -239,7 +239,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -249,12 +249,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -305,17 +299,17 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП КОМПЛЕКС ЗА ДЕТСКО ХРАНЕНЕ/ОП КОМПЛЕКС ЗА ДЕТСКО ХРАНЕНЕ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП КОМПЛЕКС ЗА ДЕТСКО ХРАНЕНЕ/ОП КОМПЛЕКС ЗА ДЕТСКО ХРАНЕНЕ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="61">
   <si>
     <t>Дата</t>
   </si>
@@ -46,10 +46,16 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
+    <t>Час</t>
+  </si>
+  <si>
     <t>Километри</t>
   </si>
   <si>
-    <t>Варна</t>
+    <t>Billing_Document</t>
+  </si>
+  <si>
+    <t>Варна Цар Освободител</t>
   </si>
   <si>
     <t>Варна Сливница</t>
@@ -116,6 +122,63 @@
   </si>
   <si>
     <t>95 EKONOMY UNLEADED</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>14:26</t>
+  </si>
+  <si>
+    <t>08:07</t>
+  </si>
+  <si>
+    <t>14:55</t>
+  </si>
+  <si>
+    <t>14:58</t>
+  </si>
+  <si>
+    <t>14:59</t>
+  </si>
+  <si>
+    <t>15:05</t>
+  </si>
+  <si>
+    <t>15:06</t>
+  </si>
+  <si>
+    <t>15:10</t>
+  </si>
+  <si>
+    <t>15:13</t>
+  </si>
+  <si>
+    <t>15:28</t>
+  </si>
+  <si>
+    <t>14:08</t>
+  </si>
+  <si>
+    <t>12:53</t>
+  </si>
+  <si>
+    <t>13:35</t>
+  </si>
+  <si>
+    <t>11:05</t>
+  </si>
+  <si>
+    <t>13:26</t>
+  </si>
+  <si>
+    <t>13:27</t>
+  </si>
+  <si>
+    <t>12:54</t>
+  </si>
+  <si>
+    <t>11:08</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОП КОМПЛЕКС ЗА ДЕТСКО ХРАНЕНЕ</t>
@@ -535,7 +598,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -548,10 +611,12 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -585,22 +650,28 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="3">
         <v>46174</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F2">
         <v>70</v>
@@ -617,25 +688,31 @@
       <c r="J2">
         <v>118.3</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="s">
+        <v>36</v>
+      </c>
+      <c r="L2">
         <v>3758</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="M2">
+        <v>271516</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
         <v>46174</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F3">
         <v>63.74</v>
@@ -652,25 +729,31 @@
       <c r="J3">
         <v>107.72</v>
       </c>
-      <c r="K3">
+      <c r="K3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L3">
         <v>189764</v>
       </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="M3">
+        <v>271587</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="3">
         <v>46176</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F4">
         <v>33.16</v>
@@ -687,25 +770,31 @@
       <c r="J4">
         <v>56.04</v>
       </c>
-      <c r="K4">
+      <c r="K4" t="s">
+        <v>38</v>
+      </c>
+      <c r="L4">
         <v>193150</v>
       </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="M4">
+        <v>137968</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="3">
         <v>46176</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F5">
         <v>28</v>
@@ -722,25 +811,31 @@
       <c r="J5">
         <v>47.32</v>
       </c>
-      <c r="K5">
+      <c r="K5" t="s">
+        <v>39</v>
+      </c>
+      <c r="L5">
         <v>289694</v>
       </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="M5">
+        <v>272182</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="3">
         <v>46176</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F6">
         <v>10.12</v>
@@ -757,25 +852,31 @@
       <c r="J6">
         <v>17.1</v>
       </c>
-      <c r="K6">
+      <c r="K6" t="s">
+        <v>40</v>
+      </c>
+      <c r="L6">
         <v>193245</v>
       </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="M6">
+        <v>272186</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="3">
         <v>46176</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F7">
         <v>58</v>
@@ -792,25 +893,31 @@
       <c r="J7">
         <v>98.02</v>
       </c>
-      <c r="K7">
+      <c r="K7" t="s">
+        <v>41</v>
+      </c>
+      <c r="L7">
         <v>103297</v>
       </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="M7">
+        <v>272188</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" s="3">
         <v>46176</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F8">
         <v>32.02</v>
@@ -827,25 +934,31 @@
       <c r="J8">
         <v>54.11</v>
       </c>
-      <c r="K8">
+      <c r="K8" t="s">
+        <v>42</v>
+      </c>
+      <c r="L8">
         <v>97768</v>
       </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="M8">
+        <v>272192</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" s="3">
         <v>46176</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F9">
         <v>36</v>
@@ -862,25 +975,31 @@
       <c r="J9">
         <v>60.84</v>
       </c>
-      <c r="K9">
+      <c r="K9" t="s">
+        <v>43</v>
+      </c>
+      <c r="L9">
         <v>277198</v>
       </c>
-    </row>
-    <row r="10" spans="1:11">
+      <c r="M9">
+        <v>272195</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" s="3">
         <v>46176</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F10">
         <v>22.28</v>
@@ -897,25 +1016,31 @@
       <c r="J10">
         <v>37.65</v>
       </c>
-      <c r="K10">
+      <c r="K10" t="s">
+        <v>44</v>
+      </c>
+      <c r="L10">
         <v>3966</v>
       </c>
-    </row>
-    <row r="11" spans="1:11">
+      <c r="M10">
+        <v>272198</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" s="3">
         <v>46176</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F11">
         <v>38</v>
@@ -932,25 +1057,31 @@
       <c r="J11">
         <v>59.66</v>
       </c>
-      <c r="K11">
-        <v>1004</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+      <c r="K11" t="s">
+        <v>45</v>
+      </c>
+      <c r="L11">
+        <v>1004.1</v>
+      </c>
+      <c r="M11">
+        <v>272201</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" s="3">
         <v>46176</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F12">
         <v>17</v>
@@ -967,25 +1098,31 @@
       <c r="J12">
         <v>28.73</v>
       </c>
-      <c r="K12">
+      <c r="K12" t="s">
+        <v>45</v>
+      </c>
+      <c r="L12">
         <v>189957</v>
       </c>
-    </row>
-    <row r="13" spans="1:11">
+      <c r="M12">
+        <v>272203</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" s="3">
         <v>46181</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F13">
         <v>35.84</v>
@@ -1002,25 +1139,31 @@
       <c r="J13">
         <v>58.78</v>
       </c>
-      <c r="K13">
+      <c r="K13" t="s">
+        <v>46</v>
+      </c>
+      <c r="L13">
         <v>298194</v>
       </c>
-    </row>
-    <row r="14" spans="1:11">
+      <c r="M13">
+        <v>273527</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" s="3">
         <v>46183</v>
       </c>
       <c r="B14" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D14" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F14">
         <v>53.02</v>
@@ -1037,25 +1180,31 @@
       <c r="J14">
         <v>86.42</v>
       </c>
-      <c r="K14">
+      <c r="K14" t="s">
+        <v>47</v>
+      </c>
+      <c r="L14">
         <v>103848</v>
       </c>
-    </row>
-    <row r="15" spans="1:11">
+      <c r="M14">
+        <v>274092</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" s="3">
         <v>46184</v>
       </c>
       <c r="B15" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C15" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D15" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F15">
         <v>50</v>
@@ -1072,25 +1221,31 @@
       <c r="J15">
         <v>81</v>
       </c>
-      <c r="K15">
+      <c r="K15" t="s">
+        <v>48</v>
+      </c>
+      <c r="L15">
         <v>190545</v>
       </c>
-    </row>
-    <row r="16" spans="1:11">
+      <c r="M15">
+        <v>111318</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16" s="3">
         <v>46184</v>
       </c>
       <c r="B16" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C16" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F16">
         <v>40</v>
@@ -1107,25 +1262,31 @@
       <c r="J16">
         <v>64.8</v>
       </c>
-      <c r="K16">
+      <c r="K16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L16">
         <v>193820</v>
       </c>
-    </row>
-    <row r="17" spans="1:11">
+      <c r="M16">
+        <v>274394</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" s="3">
         <v>46185</v>
       </c>
       <c r="B17" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C17" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F17">
         <v>68.02</v>
@@ -1142,25 +1303,31 @@
       <c r="J17">
         <v>109.51</v>
       </c>
-      <c r="K17">
-        <v>4502</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
+      <c r="K17" t="s">
+        <v>50</v>
+      </c>
+      <c r="L17">
+        <v>143275</v>
+      </c>
+      <c r="M17">
+        <v>274602</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" s="3">
         <v>46185</v>
       </c>
       <c r="B18" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C18" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D18" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F18">
         <v>18.64</v>
@@ -1177,25 +1344,31 @@
       <c r="J18">
         <v>30.01</v>
       </c>
-      <c r="K18">
+      <c r="K18" t="s">
+        <v>51</v>
+      </c>
+      <c r="L18">
         <v>98505</v>
       </c>
-    </row>
-    <row r="19" spans="1:11">
+      <c r="M18">
+        <v>274662</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" s="3">
         <v>46185</v>
       </c>
       <c r="B19" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C19" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D19" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F19">
         <v>12.21</v>
@@ -1212,25 +1385,31 @@
       <c r="J19">
         <v>19.66</v>
       </c>
-      <c r="K19">
+      <c r="K19" t="s">
+        <v>52</v>
+      </c>
+      <c r="L19">
         <v>98505</v>
       </c>
-    </row>
-    <row r="20" spans="1:11">
+      <c r="M19">
+        <v>274664</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" s="3">
         <v>46186</v>
       </c>
       <c r="B20" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C20" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D20" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E20" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F20">
         <v>51.78</v>
@@ -1247,25 +1426,31 @@
       <c r="J20">
         <v>80.78</v>
       </c>
-      <c r="K20">
+      <c r="K20" t="s">
+        <v>53</v>
+      </c>
+      <c r="L20">
         <v>54006</v>
       </c>
-    </row>
-    <row r="21" spans="1:11">
+      <c r="M20">
+        <v>112331</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" s="3">
         <v>46188</v>
       </c>
       <c r="B21" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C21" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D21" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F21">
         <v>38.9</v>
@@ -1282,13 +1467,19 @@
       <c r="J21">
         <v>62.24</v>
       </c>
-      <c r="K21">
+      <c r="K21" t="s">
+        <v>54</v>
+      </c>
+      <c r="L21">
         <v>298634</v>
       </c>
-    </row>
-    <row r="24" spans="1:11">
+      <c r="M21">
+        <v>275368</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
       <c r="A24" s="4" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
@@ -1296,18 +1487,18 @@
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:13">
       <c r="A25" s="5" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>7</v>
@@ -1316,9 +1507,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:13">
       <c r="A26" s="6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B26" s="7">
         <v>686.95</v>
@@ -1336,9 +1527,9 @@
         <v>1138.25</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:13">
       <c r="A27" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B27" s="7">
         <v>89.78</v>
@@ -1356,9 +1547,9 @@
         <v>140.44</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:13">
       <c r="A28" s="9" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="B28" s="10">
         <v>776.73</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП КОМПЛЕКС ЗА ДЕТСКО ХРАНЕНЕ/ОП КОМПЛЕКС ЗА ДЕТСКО ХРАНЕНЕ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП КОМПЛЕКС ЗА ДЕТСКО ХРАНЕНЕ/ОП КОМПЛЕКС ЗА ДЕТСКО ХРАНЕНЕ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="96">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,13 +52,19 @@
     <t>Час</t>
   </si>
   <si>
-    <t>Варна</t>
-  </si>
-  <si>
-    <t>Варна Чайка</t>
-  </si>
-  <si>
-    <t>Варна Сливница</t>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
+    <t>1199 Varna Car Osvoboditel</t>
+  </si>
+  <si>
+    <t>1158 Варна Чайка</t>
+  </si>
+  <si>
+    <t>1146 Варна Сливница</t>
   </si>
   <si>
     <t>В1745ВТ</t>
@@ -64,12 +73,12 @@
     <t>В6277РМ</t>
   </si>
   <si>
+    <t>В1749ВТ</t>
+  </si>
+  <si>
     <t>В2515ТМ</t>
   </si>
   <si>
-    <t>В1749ВТ</t>
-  </si>
-  <si>
     <t>В2516ТМ</t>
   </si>
   <si>
@@ -82,18 +91,21 @@
     <t>В1384РМ</t>
   </si>
   <si>
+    <t>В9799НН</t>
+  </si>
+  <si>
     <t>78970155027720337</t>
   </si>
   <si>
     <t>78970155027720311</t>
   </si>
   <si>
+    <t>78970155027720329</t>
+  </si>
+  <si>
     <t>78970155027720279</t>
   </si>
   <si>
-    <t>78970155027720329</t>
-  </si>
-  <si>
     <t>78970155027720287</t>
   </si>
   <si>
@@ -106,46 +118,172 @@
     <t>78970155027720295</t>
   </si>
   <si>
+    <t>78970155027720345</t>
+  </si>
+  <si>
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>2026-06-16 14:03:30</t>
-  </si>
-  <si>
-    <t>2026-06-18 15:43:06</t>
-  </si>
-  <si>
-    <t>2026-06-19 07:48:40</t>
-  </si>
-  <si>
-    <t>2026-06-19 12:58:19</t>
-  </si>
-  <si>
-    <t>2026-06-22 08:37:48</t>
-  </si>
-  <si>
-    <t>2026-06-22 15:08:44</t>
-  </si>
-  <si>
-    <t>2026-06-23 13:23:59</t>
-  </si>
-  <si>
-    <t>2026-06-24 07:20:30</t>
-  </si>
-  <si>
-    <t>2026-06-24 07:23:47</t>
-  </si>
-  <si>
-    <t>2026-06-24 14:16:25</t>
-  </si>
-  <si>
-    <t>2026-06-24 14:30:54</t>
-  </si>
-  <si>
-    <t>2026-06-25 07:42:35</t>
-  </si>
-  <si>
-    <t>2026-06-25 13:01:14</t>
+    <t>95 EKONOMY UNLEADED</t>
+  </si>
+  <si>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>14:03:00</t>
+  </si>
+  <si>
+    <t>15:43:00</t>
+  </si>
+  <si>
+    <t>12:58:00</t>
+  </si>
+  <si>
+    <t>07:49:00</t>
+  </si>
+  <si>
+    <t>08:38:00</t>
+  </si>
+  <si>
+    <t>15:09:00</t>
+  </si>
+  <si>
+    <t>13:24:00</t>
+  </si>
+  <si>
+    <t>07:23:00</t>
+  </si>
+  <si>
+    <t>14:16:00</t>
+  </si>
+  <si>
+    <t>07:20:00</t>
+  </si>
+  <si>
+    <t>14:31:00</t>
+  </si>
+  <si>
+    <t>13:01:00</t>
+  </si>
+  <si>
+    <t>07:43:00</t>
+  </si>
+  <si>
+    <t>13:29:00</t>
+  </si>
+  <si>
+    <t>18:22:00</t>
+  </si>
+  <si>
+    <t>14:02:00</t>
+  </si>
+  <si>
+    <t>13:30:00</t>
+  </si>
+  <si>
+    <t>14:42:00</t>
+  </si>
+  <si>
+    <t>14:47:00</t>
+  </si>
+  <si>
+    <t>14:53:00</t>
+  </si>
+  <si>
+    <t>14:40:00</t>
+  </si>
+  <si>
+    <t>14:28:00</t>
+  </si>
+  <si>
+    <t>14:48:00</t>
+  </si>
+  <si>
+    <t>15:05:00</t>
+  </si>
+  <si>
+    <t>14:44:00</t>
+  </si>
+  <si>
+    <t>3233445480 3233445480</t>
+  </si>
+  <si>
+    <t>3233539269 3233539269</t>
+  </si>
+  <si>
+    <t>3233581427 3233581427</t>
+  </si>
+  <si>
+    <t>3233541949 3233541949</t>
+  </si>
+  <si>
+    <t>3233715044 3233715044</t>
+  </si>
+  <si>
+    <t>3233733700 3233733700</t>
+  </si>
+  <si>
+    <t>3233748099 3233748099</t>
+  </si>
+  <si>
+    <t>3233795659 3233795659</t>
+  </si>
+  <si>
+    <t>3233796175 3233796175</t>
+  </si>
+  <si>
+    <t>3233815038 3233815038</t>
+  </si>
+  <si>
+    <t>3233823303 3233823303</t>
+  </si>
+  <si>
+    <t>3233860801 3233860801</t>
+  </si>
+  <si>
+    <t>3233864364 3233864364</t>
+  </si>
+  <si>
+    <t>3233954912 3233954912</t>
+  </si>
+  <si>
+    <t>3234061580 3234061580</t>
+  </si>
+  <si>
+    <t>3234055383 3234055383</t>
+  </si>
+  <si>
+    <t>3234063955 3234063955</t>
+  </si>
+  <si>
+    <t>3234068518 3234068518</t>
+  </si>
+  <si>
+    <t>3234110456 3234110456</t>
+  </si>
+  <si>
+    <t>3234113098 3234113098</t>
+  </si>
+  <si>
+    <t>3234113682 3234113682</t>
+  </si>
+  <si>
+    <t>3234116955 3234116955</t>
+  </si>
+  <si>
+    <t>3234117315 3234117315</t>
+  </si>
+  <si>
+    <t>3234117615 3234117615</t>
+  </si>
+  <si>
+    <t>3234117939 3234117939</t>
+  </si>
+  <si>
+    <t>3234118032 3234118032</t>
+  </si>
+  <si>
+    <t>3234118200 3234118200</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОП КОМПЛЕКС ЗА ДЕТСКО ХРАНЕНЕ</t>
@@ -565,7 +703,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -574,14 +712,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -615,533 +756,1295 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46189</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F2">
         <v>30.01</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H2">
         <v>1.56</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>46.82</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.59</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>47.72</v>
       </c>
-      <c r="K2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="L2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M2">
+        <v>1941700</v>
+      </c>
+      <c r="N2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>46191</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F3">
         <v>67.83</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3">
         <v>1.55</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>105.14</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.58</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>107.17</v>
       </c>
-      <c r="K3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="L3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M3">
+        <v>290387</v>
+      </c>
+      <c r="N3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
         <v>46192</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F4">
+        <v>50</v>
+      </c>
+      <c r="G4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H4">
+        <v>1.53</v>
+      </c>
+      <c r="I4" s="1">
+        <v>76.5</v>
+      </c>
+      <c r="J4">
+        <v>1.56</v>
+      </c>
+      <c r="K4" s="1">
+        <v>78</v>
+      </c>
+      <c r="L4" t="s">
         <v>40</v>
       </c>
-      <c r="G4" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="H4">
-        <v>61.2</v>
-      </c>
-      <c r="I4" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="J4">
-        <v>62.4</v>
-      </c>
-      <c r="K4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="M4">
+        <v>191100</v>
+      </c>
+      <c r="N4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="3">
         <v>46192</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E5" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F5">
-        <v>50</v>
-      </c>
-      <c r="G5" s="1">
+        <v>40</v>
+      </c>
+      <c r="G5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H5">
         <v>1.53</v>
       </c>
-      <c r="H5">
-        <v>76.5</v>
-      </c>
       <c r="I5" s="1">
+        <v>61.2</v>
+      </c>
+      <c r="J5">
         <v>1.56</v>
       </c>
-      <c r="J5">
-        <v>78</v>
-      </c>
-      <c r="K5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="K5" s="1">
+        <v>62.4</v>
+      </c>
+      <c r="L5" t="s">
+        <v>41</v>
+      </c>
+      <c r="M5">
+        <v>98885</v>
+      </c>
+      <c r="N5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="3">
         <v>46195</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F6">
         <v>40.1</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6">
         <v>1.49</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>59.75</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.52</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>60.95</v>
       </c>
-      <c r="K6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="L6" t="s">
+        <v>42</v>
+      </c>
+      <c r="M6">
+        <v>194490</v>
+      </c>
+      <c r="N6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="3">
         <v>46195</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E7" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F7">
         <v>50</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>37</v>
+      </c>
+      <c r="H7">
         <v>1.49</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="1">
         <v>74.5</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>1.52</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>76</v>
       </c>
-      <c r="K7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="L7" t="s">
+        <v>43</v>
+      </c>
+      <c r="M7">
+        <v>104720</v>
+      </c>
+      <c r="N7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="3">
         <v>46196</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F8">
         <v>67.66</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" t="s">
+        <v>37</v>
+      </c>
+      <c r="H8">
         <v>1.49</v>
       </c>
-      <c r="H8">
+      <c r="I8" s="1">
         <v>100.81</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8">
         <v>1.52</v>
       </c>
-      <c r="J8">
+      <c r="K8" s="1">
         <v>102.84</v>
       </c>
-      <c r="K8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="L8" t="s">
+        <v>44</v>
+      </c>
+      <c r="M8">
+        <v>5065</v>
+      </c>
+      <c r="N8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" s="3">
         <v>46197</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D9" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="E9" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F9">
-        <v>32.26</v>
-      </c>
-      <c r="G9" s="1">
+        <v>34</v>
+      </c>
+      <c r="G9" t="s">
+        <v>37</v>
+      </c>
+      <c r="H9">
         <v>1.48</v>
       </c>
-      <c r="H9">
-        <v>47.74</v>
-      </c>
       <c r="I9" s="1">
+        <v>50.32</v>
+      </c>
+      <c r="J9">
         <v>1.51</v>
       </c>
-      <c r="J9">
-        <v>48.71</v>
-      </c>
-      <c r="K9" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+      <c r="K9" s="1">
+        <v>51.34</v>
+      </c>
+      <c r="L9" t="s">
+        <v>45</v>
+      </c>
+      <c r="M9">
+        <v>277537</v>
+      </c>
+      <c r="N9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="3">
         <v>46197</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E10" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F10">
-        <v>34</v>
-      </c>
-      <c r="G10" s="1">
+        <v>7</v>
+      </c>
+      <c r="G10" t="s">
+        <v>37</v>
+      </c>
+      <c r="H10">
         <v>1.48</v>
       </c>
-      <c r="H10">
-        <v>50.32</v>
-      </c>
       <c r="I10" s="1">
+        <v>10.36</v>
+      </c>
+      <c r="J10">
         <v>1.51</v>
       </c>
-      <c r="J10">
-        <v>51.34</v>
-      </c>
-      <c r="K10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
+      <c r="K10" s="1">
+        <v>10.57</v>
+      </c>
+      <c r="L10" t="s">
+        <v>46</v>
+      </c>
+      <c r="M10">
+        <v>277629</v>
+      </c>
+      <c r="N10" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="3">
         <v>46197</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E11" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F11">
-        <v>7</v>
-      </c>
-      <c r="G11" s="1">
+        <v>32.26</v>
+      </c>
+      <c r="G11" t="s">
+        <v>37</v>
+      </c>
+      <c r="H11">
         <v>1.48</v>
       </c>
-      <c r="H11">
-        <v>10.36</v>
-      </c>
       <c r="I11" s="1">
+        <v>47.74</v>
+      </c>
+      <c r="J11">
         <v>1.51</v>
       </c>
-      <c r="J11">
-        <v>10.57</v>
-      </c>
-      <c r="K11" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+      <c r="K11" s="1">
+        <v>48.71</v>
+      </c>
+      <c r="L11" t="s">
+        <v>47</v>
+      </c>
+      <c r="M11">
+        <v>290712</v>
+      </c>
+      <c r="N11" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="3">
         <v>46197</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D12" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E12" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F12">
         <v>9.27</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12" t="s">
+        <v>37</v>
+      </c>
+      <c r="H12">
         <v>1.48</v>
       </c>
-      <c r="H12">
+      <c r="I12" s="1">
         <v>13.72</v>
       </c>
-      <c r="I12" s="1">
+      <c r="J12">
         <v>1.51</v>
       </c>
-      <c r="J12">
-        <v>14</v>
-      </c>
-      <c r="K12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
+      <c r="K12" s="1">
+        <v>14</v>
+      </c>
+      <c r="L12" t="s">
+        <v>48</v>
+      </c>
+      <c r="M12">
+        <v>290798</v>
+      </c>
+      <c r="N12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" s="3">
         <v>46198</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D13" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="E13" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F13">
-        <v>30</v>
-      </c>
-      <c r="G13" s="1">
+        <v>40</v>
+      </c>
+      <c r="G13" t="s">
+        <v>37</v>
+      </c>
+      <c r="H13">
         <v>1.48</v>
       </c>
-      <c r="H13">
-        <v>44.4</v>
-      </c>
       <c r="I13" s="1">
+        <v>59.2</v>
+      </c>
+      <c r="J13">
         <v>1.51</v>
       </c>
-      <c r="J13">
-        <v>45.3</v>
-      </c>
-      <c r="K13" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
+      <c r="K13" s="1">
+        <v>60.4</v>
+      </c>
+      <c r="L13" t="s">
+        <v>49</v>
+      </c>
+      <c r="M13">
+        <v>299200</v>
+      </c>
+      <c r="N13" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" s="3">
         <v>46198</v>
       </c>
       <c r="B14" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D14" t="s">
         <v>29</v>
       </c>
       <c r="E14" t="s">
+        <v>35</v>
+      </c>
+      <c r="F14">
         <v>30</v>
       </c>
-      <c r="F14">
+      <c r="G14" t="s">
+        <v>37</v>
+      </c>
+      <c r="H14">
+        <v>1.48</v>
+      </c>
+      <c r="I14" s="1">
+        <v>44.4</v>
+      </c>
+      <c r="J14">
+        <v>1.51</v>
+      </c>
+      <c r="K14" s="1">
+        <v>45.3</v>
+      </c>
+      <c r="L14" t="s">
+        <v>50</v>
+      </c>
+      <c r="M14">
+        <v>99340</v>
+      </c>
+      <c r="N14" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="3">
+        <v>46199</v>
+      </c>
+      <c r="B15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" t="s">
+        <v>35</v>
+      </c>
+      <c r="F15">
         <v>40</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G15" t="s">
+        <v>37</v>
+      </c>
+      <c r="H15">
         <v>1.48</v>
       </c>
-      <c r="H14">
+      <c r="I15" s="1">
         <v>59.2</v>
       </c>
-      <c r="I14" s="1">
+      <c r="J15">
         <v>1.51</v>
       </c>
-      <c r="J14">
+      <c r="K15" s="1">
         <v>60.4</v>
       </c>
-      <c r="K14" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D18" s="5" t="s">
+      <c r="L15" t="s">
+        <v>51</v>
+      </c>
+      <c r="M15">
+        <v>194950</v>
+      </c>
+      <c r="N15" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="3">
+        <v>46202</v>
+      </c>
+      <c r="B16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E16" t="s">
+        <v>36</v>
+      </c>
+      <c r="F16">
+        <v>10</v>
+      </c>
+      <c r="G16" t="s">
+        <v>37</v>
+      </c>
+      <c r="H16">
+        <v>1.47</v>
+      </c>
+      <c r="I16" s="1">
+        <v>14.7</v>
+      </c>
+      <c r="J16">
+        <v>1.5</v>
+      </c>
+      <c r="K16" s="1">
+        <v>15</v>
+      </c>
+      <c r="L16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M16">
+        <v>54561</v>
+      </c>
+      <c r="N16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" s="3">
+        <v>46202</v>
+      </c>
+      <c r="B17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" t="s">
+        <v>35</v>
+      </c>
+      <c r="F17">
+        <v>30</v>
+      </c>
+      <c r="G17" t="s">
+        <v>37</v>
+      </c>
+      <c r="H17">
+        <v>1.48</v>
+      </c>
+      <c r="I17" s="1">
+        <v>44.4</v>
+      </c>
+      <c r="J17">
+        <v>1.51</v>
+      </c>
+      <c r="K17" s="1">
+        <v>45.3</v>
+      </c>
+      <c r="L17" t="s">
+        <v>53</v>
+      </c>
+      <c r="M17">
+        <v>191479</v>
+      </c>
+      <c r="N17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" s="3">
+        <v>46202</v>
+      </c>
+      <c r="B18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" t="s">
+        <v>29</v>
+      </c>
+      <c r="E18" t="s">
+        <v>35</v>
+      </c>
+      <c r="F18">
+        <v>30</v>
+      </c>
+      <c r="G18" t="s">
+        <v>37</v>
+      </c>
+      <c r="H18">
+        <v>1.48</v>
+      </c>
+      <c r="I18" s="1">
+        <v>44.4</v>
+      </c>
+      <c r="J18">
+        <v>1.51</v>
+      </c>
+      <c r="K18" s="1">
+        <v>45.3</v>
+      </c>
+      <c r="L18" t="s">
+        <v>54</v>
+      </c>
+      <c r="M18">
+        <v>99618</v>
+      </c>
+      <c r="N18" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" s="3">
+        <v>46202</v>
+      </c>
+      <c r="B19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" t="s">
+        <v>35</v>
+      </c>
+      <c r="F19">
+        <v>61</v>
+      </c>
+      <c r="G19" t="s">
+        <v>37</v>
+      </c>
+      <c r="H19">
+        <v>1.48</v>
+      </c>
+      <c r="I19" s="1">
+        <v>90.28</v>
+      </c>
+      <c r="J19">
+        <v>1.51</v>
+      </c>
+      <c r="K19" s="1">
+        <v>92.11</v>
+      </c>
+      <c r="L19" t="s">
         <v>48</v>
       </c>
-      <c r="E18" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="6" t="s">
+      <c r="M19">
+        <v>105225</v>
+      </c>
+      <c r="N19" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B20" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E20" t="s">
+        <v>35</v>
+      </c>
+      <c r="F20">
+        <v>45.35</v>
+      </c>
+      <c r="G20" t="s">
+        <v>37</v>
+      </c>
+      <c r="H20">
+        <v>1.48</v>
+      </c>
+      <c r="I20" s="1">
+        <v>67.12</v>
+      </c>
+      <c r="J20">
+        <v>1.51</v>
+      </c>
+      <c r="K20" s="1">
+        <v>68.48</v>
+      </c>
+      <c r="L20" t="s">
+        <v>55</v>
+      </c>
+      <c r="M20">
+        <v>195160</v>
+      </c>
+      <c r="N20" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B21" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" t="s">
+        <v>28</v>
+      </c>
+      <c r="E21" t="s">
+        <v>35</v>
+      </c>
+      <c r="F21">
+        <v>33</v>
+      </c>
+      <c r="G21" t="s">
+        <v>37</v>
+      </c>
+      <c r="H21">
+        <v>1.48</v>
+      </c>
+      <c r="I21" s="1">
+        <v>48.84</v>
+      </c>
+      <c r="J21">
+        <v>1.51</v>
+      </c>
+      <c r="K21" s="1">
+        <v>49.83</v>
+      </c>
+      <c r="L21" t="s">
+        <v>56</v>
+      </c>
+      <c r="M21">
+        <v>191585</v>
+      </c>
+      <c r="N21" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B22" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D22" t="s">
+        <v>31</v>
+      </c>
+      <c r="E22" t="s">
+        <v>35</v>
+      </c>
+      <c r="F22">
+        <v>67.67</v>
+      </c>
+      <c r="G22" t="s">
+        <v>37</v>
+      </c>
+      <c r="H22">
+        <v>1.48</v>
+      </c>
+      <c r="I22" s="1">
+        <v>100.15</v>
+      </c>
+      <c r="J22">
+        <v>1.51</v>
+      </c>
+      <c r="K22" s="1">
+        <v>102.18</v>
+      </c>
+      <c r="L22" t="s">
+        <v>57</v>
+      </c>
+      <c r="M22">
+        <v>5549</v>
+      </c>
+      <c r="N22" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B23" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23" t="s">
+        <v>32</v>
+      </c>
+      <c r="E23" t="s">
+        <v>35</v>
+      </c>
+      <c r="F23">
+        <v>11.57</v>
+      </c>
+      <c r="G23" t="s">
+        <v>37</v>
+      </c>
+      <c r="H23">
+        <v>1.48</v>
+      </c>
+      <c r="I23" s="1">
+        <v>17.12</v>
+      </c>
+      <c r="J23">
+        <v>1.51</v>
+      </c>
+      <c r="K23" s="1">
+        <v>17.47</v>
+      </c>
+      <c r="L23" t="s">
+        <v>58</v>
+      </c>
+      <c r="M23">
+        <v>277781</v>
+      </c>
+      <c r="N23" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B24" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" t="s">
+        <v>25</v>
+      </c>
+      <c r="D24" t="s">
+        <v>34</v>
+      </c>
+      <c r="E24" t="s">
+        <v>36</v>
+      </c>
+      <c r="F24">
+        <v>41.82</v>
+      </c>
+      <c r="G24" t="s">
+        <v>37</v>
+      </c>
+      <c r="H24">
+        <v>1.47</v>
+      </c>
+      <c r="I24" s="1">
+        <v>61.48</v>
+      </c>
+      <c r="J24">
+        <v>1.5</v>
+      </c>
+      <c r="K24" s="1">
+        <v>62.73</v>
+      </c>
+      <c r="L24" t="s">
+        <v>59</v>
+      </c>
+      <c r="M24">
+        <v>56583</v>
+      </c>
+      <c r="N24" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B25" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25" t="s">
+        <v>29</v>
+      </c>
+      <c r="E25" t="s">
+        <v>35</v>
+      </c>
+      <c r="F25">
+        <v>44.35</v>
+      </c>
+      <c r="G25" t="s">
+        <v>37</v>
+      </c>
+      <c r="H25">
+        <v>1.48</v>
+      </c>
+      <c r="I25" s="1">
+        <v>65.64</v>
+      </c>
+      <c r="J25">
+        <v>1.51</v>
+      </c>
+      <c r="K25" s="1">
+        <v>66.97</v>
+      </c>
+      <c r="L25" t="s">
+        <v>48</v>
+      </c>
+      <c r="M25">
+        <v>99744</v>
+      </c>
+      <c r="N25" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26" t="s">
+        <v>27</v>
+      </c>
+      <c r="E26" t="s">
+        <v>35</v>
+      </c>
+      <c r="F26">
+        <v>40.29</v>
+      </c>
+      <c r="G26" t="s">
+        <v>37</v>
+      </c>
+      <c r="H26">
+        <v>1.48</v>
+      </c>
+      <c r="I26" s="1">
+        <v>59.63</v>
+      </c>
+      <c r="J26">
+        <v>1.51</v>
+      </c>
+      <c r="K26" s="1">
+        <v>60.84</v>
+      </c>
+      <c r="L26" t="s">
+        <v>60</v>
+      </c>
+      <c r="M26">
+        <v>291208</v>
+      </c>
+      <c r="N26" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B27" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D27" t="s">
+        <v>33</v>
+      </c>
+      <c r="E27" t="s">
+        <v>35</v>
+      </c>
+      <c r="F27">
+        <v>11.45</v>
+      </c>
+      <c r="G27" t="s">
+        <v>37</v>
+      </c>
+      <c r="H27">
+        <v>1.48</v>
+      </c>
+      <c r="I27" s="1">
+        <v>16.95</v>
+      </c>
+      <c r="J27">
+        <v>1.51</v>
+      </c>
+      <c r="K27" s="1">
+        <v>17.29</v>
+      </c>
+      <c r="L27" t="s">
+        <v>61</v>
+      </c>
+      <c r="M27">
+        <v>299243</v>
+      </c>
+      <c r="N27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B28" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" t="s">
+        <v>21</v>
+      </c>
+      <c r="D28" t="s">
         <v>30</v>
       </c>
-      <c r="B19" s="7">
-        <v>498.13</v>
-      </c>
-      <c r="C19" s="7">
-        <v>13</v>
-      </c>
-      <c r="D19" s="8">
-        <v>1.5066</v>
-      </c>
-      <c r="E19" s="7">
-        <v>750.46</v>
-      </c>
-      <c r="F19" s="7">
-        <v>765.4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="B20" s="10">
-        <v>498.13</v>
-      </c>
-      <c r="C20" s="10">
-        <v>13</v>
-      </c>
-      <c r="D20" s="8"/>
-      <c r="E20" s="10">
-        <v>750.46</v>
-      </c>
-      <c r="F20" s="10">
-        <v>765.4</v>
+      <c r="E28" t="s">
+        <v>35</v>
+      </c>
+      <c r="F28">
+        <v>14.43</v>
+      </c>
+      <c r="G28" t="s">
+        <v>37</v>
+      </c>
+      <c r="H28">
+        <v>1.48</v>
+      </c>
+      <c r="I28" s="1">
+        <v>21.36</v>
+      </c>
+      <c r="J28">
+        <v>1.51</v>
+      </c>
+      <c r="K28" s="1">
+        <v>21.79</v>
+      </c>
+      <c r="L28" t="s">
+        <v>62</v>
+      </c>
+      <c r="M28">
+        <v>10527</v>
+      </c>
+      <c r="N28" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33" s="7">
+        <v>927.24</v>
+      </c>
+      <c r="C33" s="7">
+        <v>25</v>
+      </c>
+      <c r="D33" s="8">
+        <v>1.4943</v>
+      </c>
+      <c r="E33" s="7">
+        <v>1385.55</v>
+      </c>
+      <c r="F33" s="7">
+        <v>1413.36</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B34" s="7">
+        <v>51.82</v>
+      </c>
+      <c r="C34" s="7">
+        <v>2</v>
+      </c>
+      <c r="D34" s="8">
+        <v>1.4701</v>
+      </c>
+      <c r="E34" s="7">
+        <v>76.18000000000001</v>
+      </c>
+      <c r="F34" s="7">
+        <v>77.73</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="B35" s="10">
+        <v>979.0599999999999</v>
+      </c>
+      <c r="C35" s="10">
+        <v>27</v>
+      </c>
+      <c r="D35" s="8"/>
+      <c r="E35" s="10">
+        <v>1461.73</v>
+      </c>
+      <c r="F35" s="10">
+        <v>1491.09</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A31:F31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП КОМПЛЕКС ЗА ДЕТСКО ХРАНЕНЕ/ОП КОМПЛЕКС ЗА ДЕТСКО ХРАНЕНЕ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП КОМПЛЕКС ЗА ДЕТСКО ХРАНЕНЕ/ОП КОМПЛЕКС ЗА ДЕТСКО ХРАНЕНЕ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="68">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,13 +55,16 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>1199 Varna Car Osvoboditel</t>
-  </si>
-  <si>
-    <t>1158 Варна Чайка</t>
-  </si>
-  <si>
-    <t>1146 Варна Сливница</t>
+    <t>Варна</t>
+  </si>
+  <si>
+    <t>Варна Чайка</t>
+  </si>
+  <si>
+    <t>Варна Сливница</t>
+  </si>
+  <si>
+    <t>Варна Порт</t>
   </si>
   <si>
     <t>В1745ВТ</t>
@@ -73,12 +73,12 @@
     <t>В6277РМ</t>
   </si>
   <si>
+    <t>В2515ТМ</t>
+  </si>
+  <si>
     <t>В1749ВТ</t>
   </si>
   <si>
-    <t>В2515ТМ</t>
-  </si>
-  <si>
     <t>В2516ТМ</t>
   </si>
   <si>
@@ -100,12 +100,12 @@
     <t>78970155027720311</t>
   </si>
   <si>
+    <t>78970155027720279</t>
+  </si>
+  <si>
     <t>78970155027720329</t>
   </si>
   <si>
-    <t>78970155027720279</t>
-  </si>
-  <si>
     <t>78970155027720287</t>
   </si>
   <si>
@@ -127,163 +127,79 @@
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>14:03:00</t>
-  </si>
-  <si>
-    <t>15:43:00</t>
-  </si>
-  <si>
-    <t>12:58:00</t>
-  </si>
-  <si>
-    <t>07:49:00</t>
-  </si>
-  <si>
-    <t>08:38:00</t>
-  </si>
-  <si>
-    <t>15:09:00</t>
-  </si>
-  <si>
-    <t>13:24:00</t>
-  </si>
-  <si>
-    <t>07:23:00</t>
-  </si>
-  <si>
-    <t>14:16:00</t>
-  </si>
-  <si>
-    <t>07:20:00</t>
-  </si>
-  <si>
-    <t>14:31:00</t>
-  </si>
-  <si>
-    <t>13:01:00</t>
-  </si>
-  <si>
-    <t>07:43:00</t>
-  </si>
-  <si>
-    <t>13:29:00</t>
-  </si>
-  <si>
-    <t>18:22:00</t>
-  </si>
-  <si>
-    <t>14:02:00</t>
-  </si>
-  <si>
-    <t>13:30:00</t>
-  </si>
-  <si>
-    <t>14:42:00</t>
-  </si>
-  <si>
-    <t>14:47:00</t>
-  </si>
-  <si>
-    <t>14:53:00</t>
-  </si>
-  <si>
-    <t>14:40:00</t>
-  </si>
-  <si>
-    <t>14:28:00</t>
-  </si>
-  <si>
-    <t>14:48:00</t>
-  </si>
-  <si>
-    <t>15:05:00</t>
-  </si>
-  <si>
-    <t>14:44:00</t>
-  </si>
-  <si>
-    <t>3233445480 3233445480</t>
-  </si>
-  <si>
-    <t>3233539269 3233539269</t>
-  </si>
-  <si>
-    <t>3233581427 3233581427</t>
-  </si>
-  <si>
-    <t>3233541949 3233541949</t>
-  </si>
-  <si>
-    <t>3233715044 3233715044</t>
-  </si>
-  <si>
-    <t>3233733700 3233733700</t>
-  </si>
-  <si>
-    <t>3233748099 3233748099</t>
-  </si>
-  <si>
-    <t>3233795659 3233795659</t>
-  </si>
-  <si>
-    <t>3233796175 3233796175</t>
-  </si>
-  <si>
-    <t>3233815038 3233815038</t>
-  </si>
-  <si>
-    <t>3233823303 3233823303</t>
-  </si>
-  <si>
-    <t>3233860801 3233860801</t>
-  </si>
-  <si>
-    <t>3233864364 3233864364</t>
-  </si>
-  <si>
-    <t>3233954912 3233954912</t>
-  </si>
-  <si>
-    <t>3234061580 3234061580</t>
-  </si>
-  <si>
-    <t>3234055383 3234055383</t>
-  </si>
-  <si>
-    <t>3234063955 3234063955</t>
-  </si>
-  <si>
-    <t>3234068518 3234068518</t>
-  </si>
-  <si>
-    <t>3234110456 3234110456</t>
-  </si>
-  <si>
-    <t>3234113098 3234113098</t>
-  </si>
-  <si>
-    <t>3234113682 3234113682</t>
-  </si>
-  <si>
-    <t>3234116955 3234116955</t>
-  </si>
-  <si>
-    <t>3234117315 3234117315</t>
-  </si>
-  <si>
-    <t>3234117615 3234117615</t>
-  </si>
-  <si>
-    <t>3234117939 3234117939</t>
-  </si>
-  <si>
-    <t>3234118032 3234118032</t>
-  </si>
-  <si>
-    <t>3234118200 3234118200</t>
+    <t>14:04</t>
+  </si>
+  <si>
+    <t>15:44</t>
+  </si>
+  <si>
+    <t>07:49</t>
+  </si>
+  <si>
+    <t>12:58</t>
+  </si>
+  <si>
+    <t>08:38</t>
+  </si>
+  <si>
+    <t>15:09</t>
+  </si>
+  <si>
+    <t>13:23</t>
+  </si>
+  <si>
+    <t>07:21</t>
+  </si>
+  <si>
+    <t>07:23</t>
+  </si>
+  <si>
+    <t>14:16</t>
+  </si>
+  <si>
+    <t>14:31</t>
+  </si>
+  <si>
+    <t>07:43</t>
+  </si>
+  <si>
+    <t>13:01</t>
+  </si>
+  <si>
+    <t>13:29</t>
+  </si>
+  <si>
+    <t>13:30</t>
+  </si>
+  <si>
+    <t>14:02</t>
+  </si>
+  <si>
+    <t>18:22</t>
+  </si>
+  <si>
+    <t>14:30</t>
+  </si>
+  <si>
+    <t>14:41</t>
+  </si>
+  <si>
+    <t>14:42</t>
+  </si>
+  <si>
+    <t>14:44</t>
+  </si>
+  <si>
+    <t>14:47</t>
+  </si>
+  <si>
+    <t>14:48</t>
+  </si>
+  <si>
+    <t>14:53</t>
+  </si>
+  <si>
+    <t>15:05</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОП КОМПЛЕКС ЗА ДЕТСКО ХРАНЕНЕ</t>
@@ -703,7 +619,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N35"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -712,17 +628,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -762,16 +677,13 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="3">
         <v>46189</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
         <v>17</v>
@@ -785,37 +697,34 @@
       <c r="F2">
         <v>30.01</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="H2">
+        <v>46.82</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.59</v>
+      </c>
+      <c r="J2">
+        <v>47.72</v>
+      </c>
+      <c r="K2" t="s">
         <v>37</v>
       </c>
-      <c r="H2">
-        <v>1.56</v>
-      </c>
-      <c r="I2" s="1">
-        <v>46.82</v>
-      </c>
-      <c r="J2">
-        <v>1.59</v>
-      </c>
-      <c r="K2" s="1">
-        <v>47.72</v>
-      </c>
-      <c r="L2" t="s">
-        <v>38</v>
+      <c r="L2">
+        <v>1941700</v>
       </c>
       <c r="M2">
-        <v>1941700</v>
-      </c>
-      <c r="N2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>275752</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
         <v>46191</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
@@ -829,37 +738,34 @@
       <c r="F3">
         <v>67.83</v>
       </c>
-      <c r="G3" t="s">
-        <v>37</v>
+      <c r="G3" s="1">
+        <v>1.55</v>
       </c>
       <c r="H3">
-        <v>1.55</v>
+        <v>105.14</v>
       </c>
       <c r="I3" s="1">
-        <v>105.14</v>
+        <v>1.58</v>
       </c>
       <c r="J3">
-        <v>1.58</v>
-      </c>
-      <c r="K3" s="1">
         <v>107.17</v>
       </c>
-      <c r="L3" t="s">
-        <v>39</v>
+      <c r="K3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L3">
+        <v>290387</v>
       </c>
       <c r="M3">
-        <v>290387</v>
-      </c>
-      <c r="N3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>276359</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="3">
         <v>46192</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
         <v>19</v>
@@ -871,34 +777,31 @@
         <v>35</v>
       </c>
       <c r="F4">
-        <v>50</v>
-      </c>
-      <c r="G4" t="s">
-        <v>37</v>
+        <v>40</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1.53</v>
       </c>
       <c r="H4">
-        <v>1.53</v>
+        <v>61.2</v>
       </c>
       <c r="I4" s="1">
-        <v>76.5</v>
+        <v>1.56</v>
       </c>
       <c r="J4">
-        <v>1.56</v>
-      </c>
-      <c r="K4" s="1">
-        <v>78</v>
-      </c>
-      <c r="L4" t="s">
-        <v>40</v>
+        <v>62.4</v>
+      </c>
+      <c r="K4" t="s">
+        <v>39</v>
+      </c>
+      <c r="L4">
+        <v>98885</v>
       </c>
       <c r="M4">
-        <v>191100</v>
-      </c>
-      <c r="N4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>276496</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="3">
         <v>46192</v>
       </c>
@@ -915,39 +818,36 @@
         <v>35</v>
       </c>
       <c r="F5">
+        <v>50</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1.53</v>
+      </c>
+      <c r="H5">
+        <v>76.5</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="J5">
+        <v>78</v>
+      </c>
+      <c r="K5" t="s">
         <v>40</v>
       </c>
-      <c r="G5" t="s">
-        <v>37</v>
-      </c>
-      <c r="H5">
-        <v>1.53</v>
-      </c>
-      <c r="I5" s="1">
-        <v>61.2</v>
-      </c>
-      <c r="J5">
-        <v>1.56</v>
-      </c>
-      <c r="K5" s="1">
-        <v>62.4</v>
-      </c>
-      <c r="L5" t="s">
-        <v>41</v>
+      <c r="L5">
+        <v>191100</v>
       </c>
       <c r="M5">
-        <v>98885</v>
-      </c>
-      <c r="N5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+        <v>115540</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="3">
         <v>46195</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
         <v>17</v>
@@ -961,37 +861,34 @@
       <c r="F6">
         <v>40.1</v>
       </c>
-      <c r="G6" t="s">
-        <v>37</v>
+      <c r="G6" s="1">
+        <v>1.49</v>
       </c>
       <c r="H6">
-        <v>1.49</v>
+        <v>59.75</v>
       </c>
       <c r="I6" s="1">
-        <v>59.75</v>
+        <v>1.52</v>
       </c>
       <c r="J6">
-        <v>1.52</v>
-      </c>
-      <c r="K6" s="1">
         <v>60.95</v>
       </c>
-      <c r="L6" t="s">
-        <v>42</v>
+      <c r="K6" t="s">
+        <v>41</v>
+      </c>
+      <c r="L6">
+        <v>194490</v>
       </c>
       <c r="M6">
-        <v>194490</v>
-      </c>
-      <c r="N6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+        <v>277302</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="3">
         <v>46195</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
         <v>21</v>
@@ -1005,37 +902,34 @@
       <c r="F7">
         <v>50</v>
       </c>
-      <c r="G7" t="s">
-        <v>37</v>
+      <c r="G7" s="1">
+        <v>1.49</v>
       </c>
       <c r="H7">
-        <v>1.49</v>
+        <v>74.5</v>
       </c>
       <c r="I7" s="1">
-        <v>74.5</v>
+        <v>1.52</v>
       </c>
       <c r="J7">
-        <v>1.52</v>
-      </c>
-      <c r="K7" s="1">
         <v>76</v>
       </c>
-      <c r="L7" t="s">
-        <v>43</v>
+      <c r="K7" t="s">
+        <v>42</v>
+      </c>
+      <c r="L7">
+        <v>104720</v>
       </c>
       <c r="M7">
-        <v>104720</v>
-      </c>
-      <c r="N7" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+        <v>277466</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" s="3">
         <v>46196</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
         <v>22</v>
@@ -1049,81 +943,75 @@
       <c r="F8">
         <v>67.66</v>
       </c>
-      <c r="G8" t="s">
-        <v>37</v>
+      <c r="G8" s="1">
+        <v>1.49</v>
       </c>
       <c r="H8">
-        <v>1.49</v>
+        <v>100.81</v>
       </c>
       <c r="I8" s="1">
-        <v>100.81</v>
+        <v>1.52</v>
       </c>
       <c r="J8">
-        <v>1.52</v>
-      </c>
-      <c r="K8" s="1">
         <v>102.84</v>
       </c>
-      <c r="L8" t="s">
-        <v>44</v>
+      <c r="K8" t="s">
+        <v>43</v>
+      </c>
+      <c r="L8">
+        <v>5065</v>
       </c>
       <c r="M8">
-        <v>5065</v>
-      </c>
-      <c r="N8" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+        <v>144904</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" s="3">
         <v>46197</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E9" t="s">
         <v>35</v>
       </c>
       <c r="F9">
-        <v>34</v>
-      </c>
-      <c r="G9" t="s">
-        <v>37</v>
+        <v>32.26</v>
+      </c>
+      <c r="G9" s="1">
+        <v>1.48</v>
       </c>
       <c r="H9">
-        <v>1.48</v>
+        <v>47.74</v>
       </c>
       <c r="I9" s="1">
-        <v>50.32</v>
+        <v>1.51</v>
       </c>
       <c r="J9">
-        <v>1.51</v>
-      </c>
-      <c r="K9" s="1">
-        <v>51.34</v>
-      </c>
-      <c r="L9" t="s">
-        <v>45</v>
+        <v>48.71</v>
+      </c>
+      <c r="K9" t="s">
+        <v>44</v>
+      </c>
+      <c r="L9">
+        <v>290712</v>
       </c>
       <c r="M9">
-        <v>277537</v>
-      </c>
-      <c r="N9" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+        <v>277866</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" s="3">
         <v>46197</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
         <v>23</v>
@@ -1135,83 +1023,77 @@
         <v>35</v>
       </c>
       <c r="F10">
-        <v>7</v>
-      </c>
-      <c r="G10" t="s">
-        <v>37</v>
+        <v>34</v>
+      </c>
+      <c r="G10" s="1">
+        <v>1.48</v>
       </c>
       <c r="H10">
-        <v>1.48</v>
+        <v>50.32</v>
       </c>
       <c r="I10" s="1">
-        <v>10.36</v>
+        <v>1.51</v>
       </c>
       <c r="J10">
-        <v>1.51</v>
-      </c>
-      <c r="K10" s="1">
-        <v>10.57</v>
-      </c>
-      <c r="L10" t="s">
-        <v>46</v>
+        <v>51.34</v>
+      </c>
+      <c r="K10" t="s">
+        <v>45</v>
+      </c>
+      <c r="L10">
+        <v>277537</v>
       </c>
       <c r="M10">
-        <v>277629</v>
-      </c>
-      <c r="N10" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+        <v>145046</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" s="3">
         <v>46197</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D11" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
         <v>35</v>
       </c>
       <c r="F11">
-        <v>32.26</v>
-      </c>
-      <c r="G11" t="s">
-        <v>37</v>
+        <v>7</v>
+      </c>
+      <c r="G11" s="1">
+        <v>1.48</v>
       </c>
       <c r="H11">
-        <v>1.48</v>
+        <v>10.36</v>
       </c>
       <c r="I11" s="1">
-        <v>47.74</v>
+        <v>1.51</v>
       </c>
       <c r="J11">
-        <v>1.51</v>
-      </c>
-      <c r="K11" s="1">
-        <v>48.71</v>
-      </c>
-      <c r="L11" t="s">
-        <v>47</v>
+        <v>10.57</v>
+      </c>
+      <c r="K11" t="s">
+        <v>46</v>
+      </c>
+      <c r="L11">
+        <v>277629</v>
       </c>
       <c r="M11">
-        <v>290712</v>
-      </c>
-      <c r="N11" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+        <v>145228</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" s="3">
         <v>46197</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12" t="s">
         <v>18</v>
@@ -1225,125 +1107,116 @@
       <c r="F12">
         <v>9.27</v>
       </c>
-      <c r="G12" t="s">
-        <v>37</v>
+      <c r="G12" s="1">
+        <v>1.48</v>
       </c>
       <c r="H12">
-        <v>1.48</v>
+        <v>13.72</v>
       </c>
       <c r="I12" s="1">
-        <v>13.72</v>
+        <v>1.51</v>
       </c>
       <c r="J12">
-        <v>1.51</v>
-      </c>
-      <c r="K12" s="1">
         <v>14</v>
       </c>
-      <c r="L12" t="s">
-        <v>48</v>
+      <c r="K12" t="s">
+        <v>47</v>
+      </c>
+      <c r="L12">
+        <v>290798</v>
       </c>
       <c r="M12">
-        <v>290798</v>
-      </c>
-      <c r="N12" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+        <v>278010</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" s="3">
         <v>46198</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D13" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E13" t="s">
         <v>35</v>
       </c>
       <c r="F13">
-        <v>40</v>
-      </c>
-      <c r="G13" t="s">
-        <v>37</v>
+        <v>30</v>
+      </c>
+      <c r="G13" s="1">
+        <v>1.48</v>
       </c>
       <c r="H13">
-        <v>1.48</v>
+        <v>44.4</v>
       </c>
       <c r="I13" s="1">
-        <v>59.2</v>
+        <v>1.51</v>
       </c>
       <c r="J13">
-        <v>1.51</v>
-      </c>
-      <c r="K13" s="1">
-        <v>60.4</v>
-      </c>
-      <c r="L13" t="s">
-        <v>49</v>
+        <v>45.3</v>
+      </c>
+      <c r="K13" t="s">
+        <v>48</v>
+      </c>
+      <c r="L13">
+        <v>99340</v>
       </c>
       <c r="M13">
-        <v>299200</v>
-      </c>
-      <c r="N13" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+        <v>278162</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" s="3">
         <v>46198</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D14" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E14" t="s">
         <v>35</v>
       </c>
       <c r="F14">
-        <v>30</v>
-      </c>
-      <c r="G14" t="s">
-        <v>37</v>
+        <v>40</v>
+      </c>
+      <c r="G14" s="1">
+        <v>1.48</v>
       </c>
       <c r="H14">
-        <v>1.48</v>
+        <v>59.2</v>
       </c>
       <c r="I14" s="1">
-        <v>44.4</v>
+        <v>1.51</v>
       </c>
       <c r="J14">
-        <v>1.51</v>
-      </c>
-      <c r="K14" s="1">
-        <v>45.3</v>
-      </c>
-      <c r="L14" t="s">
-        <v>50</v>
+        <v>60.4</v>
+      </c>
+      <c r="K14" t="s">
+        <v>49</v>
+      </c>
+      <c r="L14">
+        <v>175637</v>
       </c>
       <c r="M14">
-        <v>99340</v>
-      </c>
-      <c r="N14" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+        <v>118751</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" s="3">
         <v>46199</v>
       </c>
       <c r="B15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="s">
         <v>17</v>
@@ -1357,32 +1230,29 @@
       <c r="F15">
         <v>40</v>
       </c>
-      <c r="G15" t="s">
-        <v>37</v>
+      <c r="G15" s="1">
+        <v>1.48</v>
       </c>
       <c r="H15">
-        <v>1.48</v>
+        <v>59.2</v>
       </c>
       <c r="I15" s="1">
-        <v>59.2</v>
+        <v>1.51</v>
       </c>
       <c r="J15">
-        <v>1.51</v>
-      </c>
-      <c r="K15" s="1">
         <v>60.4</v>
       </c>
-      <c r="L15" t="s">
-        <v>51</v>
+      <c r="K15" t="s">
+        <v>50</v>
+      </c>
+      <c r="L15">
+        <v>194950</v>
       </c>
       <c r="M15">
-        <v>194950</v>
-      </c>
-      <c r="N15" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+        <v>278570</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16" s="3">
         <v>46202</v>
       </c>
@@ -1390,54 +1260,51 @@
         <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D16" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F16">
-        <v>10</v>
-      </c>
-      <c r="G16" t="s">
-        <v>37</v>
+        <v>30</v>
+      </c>
+      <c r="G16" s="1">
+        <v>1.48</v>
       </c>
       <c r="H16">
-        <v>1.47</v>
+        <v>44.4</v>
       </c>
       <c r="I16" s="1">
-        <v>14.7</v>
+        <v>1.51</v>
       </c>
       <c r="J16">
-        <v>1.5</v>
-      </c>
-      <c r="K16" s="1">
-        <v>15</v>
-      </c>
-      <c r="L16" t="s">
-        <v>52</v>
+        <v>45.3</v>
+      </c>
+      <c r="K16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L16">
+        <v>187636</v>
       </c>
       <c r="M16">
-        <v>54561</v>
-      </c>
-      <c r="N16" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
+        <v>279308</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" s="3">
         <v>46202</v>
       </c>
       <c r="B17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D17" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E17" t="s">
         <v>35</v>
@@ -1445,76 +1312,70 @@
       <c r="F17">
         <v>30</v>
       </c>
-      <c r="G17" t="s">
-        <v>37</v>
+      <c r="G17" s="1">
+        <v>1.48</v>
       </c>
       <c r="H17">
-        <v>1.48</v>
+        <v>44.4</v>
       </c>
       <c r="I17" s="1">
-        <v>44.4</v>
+        <v>1.51</v>
       </c>
       <c r="J17">
-        <v>1.51</v>
-      </c>
-      <c r="K17" s="1">
         <v>45.3</v>
       </c>
-      <c r="L17" t="s">
-        <v>53</v>
+      <c r="K17" t="s">
+        <v>52</v>
+      </c>
+      <c r="L17">
+        <v>191479</v>
       </c>
       <c r="M17">
-        <v>191479</v>
-      </c>
-      <c r="N17" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
+        <v>279319</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" s="3">
         <v>46202</v>
       </c>
       <c r="B18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D18" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E18" t="s">
         <v>35</v>
       </c>
       <c r="F18">
-        <v>30</v>
-      </c>
-      <c r="G18" t="s">
-        <v>37</v>
+        <v>61</v>
+      </c>
+      <c r="G18" s="1">
+        <v>1.48</v>
       </c>
       <c r="H18">
-        <v>1.48</v>
+        <v>90.28</v>
       </c>
       <c r="I18" s="1">
-        <v>44.4</v>
+        <v>1.51</v>
       </c>
       <c r="J18">
-        <v>1.51</v>
-      </c>
-      <c r="K18" s="1">
-        <v>45.3</v>
-      </c>
-      <c r="L18" t="s">
-        <v>54</v>
+        <v>92.11</v>
+      </c>
+      <c r="K18" t="s">
+        <v>47</v>
+      </c>
+      <c r="L18">
+        <v>105225</v>
       </c>
       <c r="M18">
-        <v>99618</v>
-      </c>
-      <c r="N18" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
+        <v>279334</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" s="3">
         <v>46202</v>
       </c>
@@ -1522,92 +1383,86 @@
         <v>14</v>
       </c>
       <c r="C19" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D19" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F19">
-        <v>61</v>
-      </c>
-      <c r="G19" t="s">
-        <v>37</v>
+        <v>10</v>
+      </c>
+      <c r="G19" s="1">
+        <v>1.47</v>
       </c>
       <c r="H19">
-        <v>1.48</v>
+        <v>14.7</v>
       </c>
       <c r="I19" s="1">
-        <v>90.28</v>
+        <v>1.5</v>
       </c>
       <c r="J19">
-        <v>1.51</v>
-      </c>
-      <c r="K19" s="1">
-        <v>92.11</v>
-      </c>
-      <c r="L19" t="s">
-        <v>48</v>
+        <v>15</v>
+      </c>
+      <c r="K19" t="s">
+        <v>53</v>
+      </c>
+      <c r="L19">
+        <v>54561</v>
       </c>
       <c r="M19">
-        <v>105225</v>
-      </c>
-      <c r="N19" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
+        <v>121227</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" s="3">
         <v>46203</v>
       </c>
       <c r="B20" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C20" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D20" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E20" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F20">
-        <v>45.35</v>
-      </c>
-      <c r="G20" t="s">
-        <v>37</v>
+        <v>41.82</v>
+      </c>
+      <c r="G20" s="1">
+        <v>1.47</v>
       </c>
       <c r="H20">
-        <v>1.48</v>
+        <v>61.48</v>
       </c>
       <c r="I20" s="1">
-        <v>67.12</v>
+        <v>1.5</v>
       </c>
       <c r="J20">
-        <v>1.51</v>
-      </c>
-      <c r="K20" s="1">
-        <v>68.48</v>
-      </c>
-      <c r="L20" t="s">
-        <v>55</v>
+        <v>62.73</v>
+      </c>
+      <c r="K20" t="s">
+        <v>54</v>
+      </c>
+      <c r="L20">
+        <v>56583</v>
       </c>
       <c r="M20">
-        <v>195160</v>
-      </c>
-      <c r="N20" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
+        <v>279636</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" s="3">
         <v>46203</v>
       </c>
       <c r="B21" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C21" t="s">
         <v>19</v>
@@ -1619,171 +1474,159 @@
         <v>35</v>
       </c>
       <c r="F21">
-        <v>33</v>
-      </c>
-      <c r="G21" t="s">
-        <v>37</v>
+        <v>44.35</v>
+      </c>
+      <c r="G21" s="1">
+        <v>1.48</v>
       </c>
       <c r="H21">
-        <v>1.48</v>
+        <v>65.64</v>
       </c>
       <c r="I21" s="1">
-        <v>48.84</v>
+        <v>1.51</v>
       </c>
       <c r="J21">
-        <v>1.51</v>
-      </c>
-      <c r="K21" s="1">
-        <v>49.83</v>
-      </c>
-      <c r="L21" t="s">
-        <v>56</v>
+        <v>66.97</v>
+      </c>
+      <c r="K21" t="s">
+        <v>47</v>
+      </c>
+      <c r="L21">
+        <v>99744</v>
       </c>
       <c r="M21">
-        <v>191585</v>
-      </c>
-      <c r="N21" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14">
+        <v>279640</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" s="3">
         <v>46203</v>
       </c>
       <c r="B22" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E22" t="s">
         <v>35</v>
       </c>
       <c r="F22">
-        <v>67.67</v>
-      </c>
-      <c r="G22" t="s">
-        <v>37</v>
+        <v>11.57</v>
+      </c>
+      <c r="G22" s="1">
+        <v>1.48</v>
       </c>
       <c r="H22">
-        <v>1.48</v>
+        <v>17.12</v>
       </c>
       <c r="I22" s="1">
-        <v>100.15</v>
+        <v>1.51</v>
       </c>
       <c r="J22">
-        <v>1.51</v>
-      </c>
-      <c r="K22" s="1">
-        <v>102.18</v>
-      </c>
-      <c r="L22" t="s">
-        <v>57</v>
+        <v>17.47</v>
+      </c>
+      <c r="K22" t="s">
+        <v>55</v>
+      </c>
+      <c r="L22">
+        <v>277781</v>
       </c>
       <c r="M22">
-        <v>5549</v>
-      </c>
-      <c r="N22" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14">
+        <v>279647</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23" s="3">
         <v>46203</v>
       </c>
       <c r="B23" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C23" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D23" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E23" t="s">
         <v>35</v>
       </c>
       <c r="F23">
-        <v>11.57</v>
-      </c>
-      <c r="G23" t="s">
-        <v>37</v>
+        <v>45.35</v>
+      </c>
+      <c r="G23" s="1">
+        <v>1.48</v>
       </c>
       <c r="H23">
-        <v>1.48</v>
+        <v>67.12</v>
       </c>
       <c r="I23" s="1">
-        <v>17.12</v>
+        <v>1.51</v>
       </c>
       <c r="J23">
-        <v>1.51</v>
-      </c>
-      <c r="K23" s="1">
-        <v>17.47</v>
-      </c>
-      <c r="L23" t="s">
-        <v>58</v>
+        <v>68.48</v>
+      </c>
+      <c r="K23" t="s">
+        <v>56</v>
+      </c>
+      <c r="L23">
+        <v>195160</v>
       </c>
       <c r="M23">
-        <v>277781</v>
-      </c>
-      <c r="N23" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14">
+        <v>279651</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
       <c r="A24" s="3">
         <v>46203</v>
       </c>
       <c r="B24" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C24" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D24" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E24" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F24">
-        <v>41.82</v>
-      </c>
-      <c r="G24" t="s">
-        <v>37</v>
+        <v>14.43</v>
+      </c>
+      <c r="G24" s="1">
+        <v>1.48</v>
       </c>
       <c r="H24">
-        <v>1.47</v>
+        <v>21.36</v>
       </c>
       <c r="I24" s="1">
-        <v>61.48</v>
+        <v>1.51</v>
       </c>
       <c r="J24">
-        <v>1.5</v>
-      </c>
-      <c r="K24" s="1">
-        <v>62.73</v>
-      </c>
-      <c r="L24" t="s">
-        <v>59</v>
+        <v>21.79</v>
+      </c>
+      <c r="K24" t="s">
+        <v>57</v>
+      </c>
+      <c r="L24">
+        <v>10527</v>
       </c>
       <c r="M24">
-        <v>56583</v>
-      </c>
-      <c r="N24" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14">
+        <v>279654</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
       <c r="A25" s="3">
         <v>46203</v>
       </c>
       <c r="B25" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C25" t="s">
         <v>20</v>
@@ -1795,39 +1638,36 @@
         <v>35</v>
       </c>
       <c r="F25">
-        <v>44.35</v>
-      </c>
-      <c r="G25" t="s">
-        <v>37</v>
+        <v>33</v>
+      </c>
+      <c r="G25" s="1">
+        <v>1.48</v>
       </c>
       <c r="H25">
-        <v>1.48</v>
+        <v>48.84</v>
       </c>
       <c r="I25" s="1">
-        <v>65.64</v>
+        <v>1.51</v>
       </c>
       <c r="J25">
-        <v>1.51</v>
-      </c>
-      <c r="K25" s="1">
-        <v>66.97</v>
-      </c>
-      <c r="L25" t="s">
-        <v>48</v>
+        <v>49.83</v>
+      </c>
+      <c r="K25" t="s">
+        <v>58</v>
+      </c>
+      <c r="L25">
+        <v>191585</v>
       </c>
       <c r="M25">
-        <v>99744</v>
-      </c>
-      <c r="N25" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14">
+        <v>279658</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
       <c r="A26" s="3">
         <v>46203</v>
       </c>
       <c r="B26" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C26" t="s">
         <v>18</v>
@@ -1841,122 +1681,113 @@
       <c r="F26">
         <v>40.29</v>
       </c>
-      <c r="G26" t="s">
-        <v>37</v>
+      <c r="G26" s="1">
+        <v>1.48</v>
       </c>
       <c r="H26">
-        <v>1.48</v>
+        <v>59.63</v>
       </c>
       <c r="I26" s="1">
-        <v>59.63</v>
+        <v>1.51</v>
       </c>
       <c r="J26">
-        <v>1.51</v>
-      </c>
-      <c r="K26" s="1">
         <v>60.84</v>
       </c>
-      <c r="L26" t="s">
-        <v>60</v>
+      <c r="K26" t="s">
+        <v>59</v>
+      </c>
+      <c r="L26">
+        <v>291208</v>
       </c>
       <c r="M26">
-        <v>291208</v>
-      </c>
-      <c r="N26" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14">
+        <v>279660</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
       <c r="A27" s="3">
         <v>46203</v>
       </c>
       <c r="B27" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C27" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D27" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E27" t="s">
         <v>35</v>
       </c>
       <c r="F27">
-        <v>11.45</v>
-      </c>
-      <c r="G27" t="s">
-        <v>37</v>
+        <v>67.67</v>
+      </c>
+      <c r="G27" s="1">
+        <v>1.48</v>
       </c>
       <c r="H27">
-        <v>1.48</v>
+        <v>100.15</v>
       </c>
       <c r="I27" s="1">
-        <v>16.95</v>
+        <v>1.51</v>
       </c>
       <c r="J27">
-        <v>1.51</v>
-      </c>
-      <c r="K27" s="1">
-        <v>17.29</v>
-      </c>
-      <c r="L27" t="s">
-        <v>61</v>
+        <v>102.18</v>
+      </c>
+      <c r="K27" t="s">
+        <v>60</v>
+      </c>
+      <c r="L27">
+        <v>5549</v>
       </c>
       <c r="M27">
-        <v>299243</v>
-      </c>
-      <c r="N27" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14">
+        <v>279662</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
       <c r="A28" s="3">
         <v>46203</v>
       </c>
       <c r="B28" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C28" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D28" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E28" t="s">
         <v>35</v>
       </c>
       <c r="F28">
-        <v>14.43</v>
-      </c>
-      <c r="G28" t="s">
-        <v>37</v>
+        <v>11.45</v>
+      </c>
+      <c r="G28" s="1">
+        <v>1.48</v>
       </c>
       <c r="H28">
-        <v>1.48</v>
+        <v>16.95</v>
       </c>
       <c r="I28" s="1">
-        <v>21.36</v>
+        <v>1.51</v>
       </c>
       <c r="J28">
-        <v>1.51</v>
-      </c>
-      <c r="K28" s="1">
-        <v>21.79</v>
-      </c>
-      <c r="L28" t="s">
+        <v>17.29</v>
+      </c>
+      <c r="K28" t="s">
+        <v>61</v>
+      </c>
+      <c r="L28">
+        <v>299243</v>
+      </c>
+      <c r="M28">
+        <v>279666</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
+      <c r="A31" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="M28">
-        <v>10527</v>
-      </c>
-      <c r="N28" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14">
-      <c r="A31" s="4" t="s">
-        <v>90</v>
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
@@ -1964,24 +1795,24 @@
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
     </row>
-    <row r="32" spans="1:14">
+    <row r="32" spans="1:13">
       <c r="A32" s="5" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>92</v>
+        <v>64</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>93</v>
+        <v>65</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -2026,7 +1857,7 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="9" t="s">
-        <v>95</v>
+        <v>67</v>
       </c>
       <c r="B35" s="10">
         <v>979.0599999999999</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП КОМПЛЕКС ЗА ДЕТСКО ХРАНЕНЕ/ОП КОМПЛЕКС ЗА ДЕТСКО ХРАНЕНЕ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП КОМПЛЕКС ЗА ДЕТСКО ХРАНЕНЕ/ОП КОМПЛЕКС ЗА ДЕТСКО ХРАНЕНЕ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="83">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,106 +55,196 @@
     <t>Километри</t>
   </si>
   <si>
-    <t>Варна Сливница</t>
-  </si>
-  <si>
-    <t>Варна Порт</t>
-  </si>
-  <si>
-    <t>Варна</t>
-  </si>
-  <si>
-    <t>Варна Чайка</t>
+    <t>Billing_Document</t>
+  </si>
+  <si>
+    <t>1158 Варна Чайка</t>
+  </si>
+  <si>
+    <t>1199 Varna Car Osvoboditel</t>
+  </si>
+  <si>
+    <t>1146 Варна Сливница</t>
+  </si>
+  <si>
+    <t>В2516ТМ</t>
+  </si>
+  <si>
+    <t>В1745ВТ</t>
+  </si>
+  <si>
+    <t>В1749ВТ</t>
+  </si>
+  <si>
+    <t>В6277РМ</t>
+  </si>
+  <si>
+    <t>В1384РМ</t>
+  </si>
+  <si>
+    <t>В9799НН</t>
   </si>
   <si>
     <t>B8393XK</t>
   </si>
   <si>
-    <t>В1745ВТ</t>
-  </si>
-  <si>
-    <t>В2516ТМ</t>
-  </si>
-  <si>
     <t>В8011КН</t>
   </si>
   <si>
-    <t>В6277РМ</t>
-  </si>
-  <si>
-    <t>В2515ТМ</t>
-  </si>
-  <si>
-    <t>В1384РМ</t>
-  </si>
-  <si>
-    <t>В9799НН</t>
+    <t>78970155027720287</t>
+  </si>
+  <si>
+    <t>78970155027720337</t>
+  </si>
+  <si>
+    <t>78970155027720329</t>
+  </si>
+  <si>
+    <t>78970155027720311</t>
+  </si>
+  <si>
+    <t>78970155027720295</t>
+  </si>
+  <si>
+    <t>78970155027720345</t>
   </si>
   <si>
     <t>78970155027720261</t>
   </si>
   <si>
-    <t>78970155027720337</t>
-  </si>
-  <si>
-    <t>78970155027720287</t>
-  </si>
-  <si>
     <t>78970155027720303</t>
   </si>
   <si>
-    <t>78970155027720311</t>
-  </si>
-  <si>
-    <t>78970155027720279</t>
-  </si>
-  <si>
-    <t>78970155027720295</t>
-  </si>
-  <si>
-    <t>78970155027720345</t>
-  </si>
-  <si>
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>DIESEL DOUBLE FILTERED</t>
-  </si>
-  <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>2026-07-08 07:57:03</t>
-  </si>
-  <si>
-    <t>2026-07-08 12:44:32</t>
-  </si>
-  <si>
-    <t>2026-07-09 14:32:23</t>
-  </si>
-  <si>
-    <t>2026-07-10 12:50:21</t>
-  </si>
-  <si>
-    <t>2026-07-10 14:18:32</t>
-  </si>
-  <si>
-    <t>2026-07-14 12:28:58</t>
-  </si>
-  <si>
-    <t>2026-07-14 13:31:18</t>
-  </si>
-  <si>
-    <t>2026-07-14 13:53:57</t>
-  </si>
-  <si>
-    <t>2026-07-14 13:53:58</t>
-  </si>
-  <si>
-    <t>2026-07-15 14:45:35</t>
-  </si>
-  <si>
-    <t>2026-07-15 17:27:22</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>11:52:00</t>
+  </si>
+  <si>
+    <t>08:55:00</t>
+  </si>
+  <si>
+    <t>13:04:00</t>
+  </si>
+  <si>
+    <t>14:58:00</t>
+  </si>
+  <si>
+    <t>14:30:00</t>
+  </si>
+  <si>
+    <t>11:40:00</t>
+  </si>
+  <si>
+    <t>17:13:00</t>
+  </si>
+  <si>
+    <t>13:18:00</t>
+  </si>
+  <si>
+    <t>13:30:00</t>
+  </si>
+  <si>
+    <t>13:13:00</t>
+  </si>
+  <si>
+    <t>07:51:00</t>
+  </si>
+  <si>
+    <t>07:29:00</t>
+  </si>
+  <si>
+    <t>14:06:00</t>
+  </si>
+  <si>
+    <t>15:16:00</t>
+  </si>
+  <si>
+    <t>08:00:00</t>
+  </si>
+  <si>
+    <t>15:08:00</t>
+  </si>
+  <si>
+    <t>15:05:00</t>
+  </si>
+  <si>
+    <t>15:04:00</t>
+  </si>
+  <si>
+    <t>15:12:00</t>
+  </si>
+  <si>
+    <t>14:59:00</t>
+  </si>
+  <si>
+    <t>3234847229 3234847229</t>
+  </si>
+  <si>
+    <t>3234953530 3234953530</t>
+  </si>
+  <si>
+    <t>3235095666 3235095666</t>
+  </si>
+  <si>
+    <t>3235098575 3235098575</t>
+  </si>
+  <si>
+    <t>3235103660 3235103660</t>
+  </si>
+  <si>
+    <t>3235188186 3235188186</t>
+  </si>
+  <si>
+    <t>3235197185 3235197185</t>
+  </si>
+  <si>
+    <t>3235240597 3235240597</t>
+  </si>
+  <si>
+    <t>3235305707 3235305707</t>
+  </si>
+  <si>
+    <t>3235437727 3235437727</t>
+  </si>
+  <si>
+    <t>3235484882 3235484882</t>
+  </si>
+  <si>
+    <t>3235509731 3235509731</t>
+  </si>
+  <si>
+    <t>3235598118 3235598118</t>
+  </si>
+  <si>
+    <t>3235646467 3235646467</t>
+  </si>
+  <si>
+    <t>3235650425 3235650425</t>
+  </si>
+  <si>
+    <t>3235654244 3235654244</t>
+  </si>
+  <si>
+    <t>3235654481 3235654481</t>
+  </si>
+  <si>
+    <t>3235657067 3235657067</t>
+  </si>
+  <si>
+    <t>3235657274 3235657274</t>
+  </si>
+  <si>
+    <t>3235657836 3235657836</t>
+  </si>
+  <si>
+    <t>3235658325 3235658325</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОП КОМПЛЕКС ЗА ДЕТСКО ХРАНЕНЕ</t>
@@ -571,7 +664,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:N29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -580,15 +673,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -625,203 +720,239 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
-        <v>46211</v>
+        <v>46219</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F2">
-        <v>67.48</v>
-      </c>
-      <c r="G2" s="1">
-        <v>1.49</v>
+        <v>46</v>
+      </c>
+      <c r="G2" t="s">
+        <v>35</v>
       </c>
       <c r="H2">
-        <v>100.55</v>
+        <v>1.58</v>
       </c>
       <c r="I2" s="1">
-        <v>1.52</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="J2">
-        <v>102.57</v>
-      </c>
-      <c r="K2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L2">
-        <v>6068</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+        <v>1.61</v>
+      </c>
+      <c r="K2" s="1">
+        <v>74.06</v>
+      </c>
+      <c r="L2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M2">
+        <v>106588</v>
+      </c>
+      <c r="N2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
-        <v>46211</v>
+        <v>46220</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F3">
-        <v>50</v>
-      </c>
-      <c r="G3" s="1">
-        <v>1.49</v>
+        <v>40</v>
+      </c>
+      <c r="G3" t="s">
+        <v>35</v>
       </c>
       <c r="H3">
-        <v>74.5</v>
+        <v>1.6</v>
       </c>
       <c r="I3" s="1">
-        <v>1.52</v>
+        <v>64</v>
       </c>
       <c r="J3">
-        <v>76</v>
-      </c>
-      <c r="K3" t="s">
-        <v>36</v>
-      </c>
-      <c r="L3">
-        <v>195800</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+        <v>1.63</v>
+      </c>
+      <c r="K3" s="1">
+        <v>65.2</v>
+      </c>
+      <c r="L3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M3">
+        <v>196470</v>
+      </c>
+      <c r="N3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
-        <v>46212</v>
+        <v>46223</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F4">
-        <v>60</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1.49</v>
+        <v>50</v>
+      </c>
+      <c r="G4" t="s">
+        <v>35</v>
       </c>
       <c r="H4">
-        <v>89.40000000000001</v>
+        <v>1.65</v>
       </c>
       <c r="I4" s="1">
-        <v>1.52</v>
+        <v>82.5</v>
       </c>
       <c r="J4">
-        <v>91.2</v>
-      </c>
-      <c r="K4" t="s">
-        <v>37</v>
-      </c>
-      <c r="L4">
-        <v>105041</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+        <v>1.68</v>
+      </c>
+      <c r="K4" s="1">
+        <v>84</v>
+      </c>
+      <c r="L4" t="s">
+        <v>38</v>
+      </c>
+      <c r="M4">
+        <v>192174</v>
+      </c>
+      <c r="N4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="3">
-        <v>46213</v>
+        <v>46223</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F5">
-        <v>40.97</v>
-      </c>
-      <c r="G5" s="1">
-        <v>1.51</v>
+        <v>61.21</v>
+      </c>
+      <c r="G5" t="s">
+        <v>35</v>
       </c>
       <c r="H5">
-        <v>61.86</v>
+        <v>1.65</v>
       </c>
       <c r="I5" s="1">
-        <v>1.54</v>
+        <v>101</v>
       </c>
       <c r="J5">
-        <v>63.09</v>
-      </c>
-      <c r="K5" t="s">
-        <v>38</v>
-      </c>
-      <c r="L5">
-        <v>278269</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+        <v>1.68</v>
+      </c>
+      <c r="K5" s="1">
+        <v>102.83</v>
+      </c>
+      <c r="L5" t="s">
+        <v>39</v>
+      </c>
+      <c r="M5">
+        <v>292456</v>
+      </c>
+      <c r="N5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="3">
-        <v>46213</v>
+        <v>46223</v>
       </c>
       <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6">
+        <v>34.17</v>
+      </c>
+      <c r="G6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6">
+        <v>1.65</v>
+      </c>
+      <c r="I6" s="1">
+        <v>56.38</v>
+      </c>
+      <c r="J6">
+        <v>1.68</v>
+      </c>
+      <c r="K6" s="1">
+        <v>57.41</v>
+      </c>
+      <c r="L6" t="s">
+        <v>40</v>
+      </c>
+      <c r="M6">
+        <v>300120</v>
+      </c>
+      <c r="N6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B7" t="s">
         <v>14</v>
-      </c>
-      <c r="C6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F6">
-        <v>64.95</v>
-      </c>
-      <c r="G6" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="H6">
-        <v>98.06999999999999</v>
-      </c>
-      <c r="I6" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="J6">
-        <v>100.02</v>
-      </c>
-      <c r="K6" t="s">
-        <v>39</v>
-      </c>
-      <c r="L6">
-        <v>291832</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="3">
-        <v>46217</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
       </c>
       <c r="C7" t="s">
         <v>17</v>
@@ -830,185 +961,215 @@
         <v>25</v>
       </c>
       <c r="E7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F7">
-        <v>40</v>
-      </c>
-      <c r="G7" s="1">
-        <v>1.53</v>
+        <v>42.02</v>
+      </c>
+      <c r="G7" t="s">
+        <v>35</v>
       </c>
       <c r="H7">
-        <v>61.2</v>
+        <v>1.66</v>
       </c>
       <c r="I7" s="1">
-        <v>1.56</v>
+        <v>69.75</v>
       </c>
       <c r="J7">
-        <v>62.4</v>
-      </c>
-      <c r="K7" t="s">
-        <v>40</v>
-      </c>
-      <c r="L7">
-        <v>196230</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
+        <v>1.69</v>
+      </c>
+      <c r="K7" s="1">
+        <v>71.01000000000001</v>
+      </c>
+      <c r="L7" t="s">
+        <v>41</v>
+      </c>
+      <c r="M7">
+        <v>106052</v>
+      </c>
+      <c r="N7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="3">
-        <v>46217</v>
+        <v>46225</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F8">
-        <v>30.01</v>
-      </c>
-      <c r="G8" s="1">
-        <v>1.53</v>
+        <v>30</v>
+      </c>
+      <c r="G8" t="s">
+        <v>35</v>
       </c>
       <c r="H8">
-        <v>45.92</v>
+        <v>1.51</v>
       </c>
       <c r="I8" s="1">
-        <v>1.56</v>
+        <v>45.3</v>
       </c>
       <c r="J8">
-        <v>46.82</v>
-      </c>
-      <c r="K8" t="s">
-        <v>41</v>
-      </c>
-      <c r="L8">
-        <v>100466</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
+        <v>1.54</v>
+      </c>
+      <c r="K8" s="1">
+        <v>46.2</v>
+      </c>
+      <c r="L8" t="s">
+        <v>42</v>
+      </c>
+      <c r="M8">
+        <v>55280</v>
+      </c>
+      <c r="N8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" s="3">
-        <v>46217</v>
+        <v>46226</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E9" t="s">
         <v>33</v>
       </c>
       <c r="F9">
-        <v>9.5</v>
-      </c>
-      <c r="G9" s="1">
-        <v>1.79</v>
+        <v>40</v>
+      </c>
+      <c r="G9" t="s">
+        <v>35</v>
       </c>
       <c r="H9">
-        <v>17</v>
+        <v>1.67</v>
       </c>
       <c r="I9" s="1">
-        <v>1.82</v>
+        <v>66.8</v>
       </c>
       <c r="J9">
-        <v>17.29</v>
-      </c>
-      <c r="K9" t="s">
-        <v>42</v>
-      </c>
-      <c r="L9">
-        <v>299737</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
+        <v>1.7</v>
+      </c>
+      <c r="K9" s="1">
+        <v>68</v>
+      </c>
+      <c r="L9" t="s">
+        <v>43</v>
+      </c>
+      <c r="M9">
+        <v>7200</v>
+      </c>
+      <c r="N9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="3">
-        <v>46217</v>
+        <v>46227</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D10" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F10">
-        <v>35.31</v>
-      </c>
-      <c r="G10" s="1">
-        <v>1.53</v>
+        <v>40</v>
+      </c>
+      <c r="G10" t="s">
+        <v>35</v>
       </c>
       <c r="H10">
-        <v>54.02</v>
+        <v>1.69</v>
       </c>
       <c r="I10" s="1">
-        <v>1.56</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="J10">
-        <v>55.08</v>
-      </c>
-      <c r="K10" t="s">
-        <v>43</v>
-      </c>
-      <c r="L10">
-        <v>299737</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
+        <v>1.72</v>
+      </c>
+      <c r="K10" s="1">
+        <v>68.8</v>
+      </c>
+      <c r="L10" t="s">
+        <v>44</v>
+      </c>
+      <c r="M10">
+        <v>196940</v>
+      </c>
+      <c r="N10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="3">
-        <v>46218</v>
+        <v>46230</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D11" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F11">
-        <v>69</v>
-      </c>
-      <c r="G11" s="1">
-        <v>1.55</v>
+        <v>50</v>
+      </c>
+      <c r="G11" t="s">
+        <v>35</v>
       </c>
       <c r="H11">
-        <v>106.95</v>
+        <v>1.72</v>
       </c>
       <c r="I11" s="1">
-        <v>1.58</v>
+        <v>86</v>
       </c>
       <c r="J11">
-        <v>109.02</v>
-      </c>
-      <c r="K11" t="s">
-        <v>44</v>
-      </c>
-      <c r="L11">
-        <v>6602</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
+        <v>1.75</v>
+      </c>
+      <c r="K11" s="1">
+        <v>87.5</v>
+      </c>
+      <c r="L11" t="s">
+        <v>45</v>
+      </c>
+      <c r="M11">
+        <v>192695</v>
+      </c>
+      <c r="N11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="3">
-        <v>46218</v>
+        <v>46231</v>
       </c>
       <c r="B12" t="s">
         <v>15</v>
@@ -1020,141 +1181,567 @@
         <v>31</v>
       </c>
       <c r="E12" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12">
+        <v>40</v>
+      </c>
+      <c r="G12" t="s">
+        <v>35</v>
+      </c>
+      <c r="H12">
+        <v>1.72</v>
+      </c>
+      <c r="I12" s="1">
+        <v>68.8</v>
+      </c>
+      <c r="J12">
+        <v>1.75</v>
+      </c>
+      <c r="K12" s="1">
+        <v>70</v>
+      </c>
+      <c r="L12" t="s">
+        <v>46</v>
+      </c>
+      <c r="M12">
+        <v>7474</v>
+      </c>
+      <c r="N12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="3">
+        <v>46232</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13">
+        <v>47.17</v>
+      </c>
+      <c r="G13" t="s">
+        <v>35</v>
+      </c>
+      <c r="H13">
+        <v>1.72</v>
+      </c>
+      <c r="I13" s="1">
+        <v>81.13</v>
+      </c>
+      <c r="J13">
+        <v>1.75</v>
+      </c>
+      <c r="K13" s="1">
+        <v>82.55</v>
+      </c>
+      <c r="L13" t="s">
+        <v>47</v>
+      </c>
+      <c r="M13">
+        <v>300679</v>
+      </c>
+      <c r="N13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="3">
+        <v>46233</v>
+      </c>
+      <c r="B14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14">
+        <v>40</v>
+      </c>
+      <c r="G14" t="s">
+        <v>35</v>
+      </c>
+      <c r="H14">
+        <v>1.73</v>
+      </c>
+      <c r="I14" s="1">
+        <v>69.2</v>
+      </c>
+      <c r="J14">
+        <v>1.76</v>
+      </c>
+      <c r="K14" s="1">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="L14" t="s">
+        <v>48</v>
+      </c>
+      <c r="M14">
+        <v>197370</v>
+      </c>
+      <c r="N14" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="3">
+        <v>46234</v>
+      </c>
+      <c r="B15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" t="s">
         <v>34</v>
       </c>
-      <c r="F12">
+      <c r="F15">
+        <v>38</v>
+      </c>
+      <c r="G15" t="s">
+        <v>35</v>
+      </c>
+      <c r="H15">
+        <v>1.52</v>
+      </c>
+      <c r="I15" s="1">
+        <v>57.76</v>
+      </c>
+      <c r="J15">
+        <v>1.55</v>
+      </c>
+      <c r="K15" s="1">
+        <v>58.9</v>
+      </c>
+      <c r="L15" t="s">
+        <v>49</v>
+      </c>
+      <c r="M15">
+        <v>55436</v>
+      </c>
+      <c r="N15" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="3">
+        <v>46234</v>
+      </c>
+      <c r="B16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16" t="s">
+        <v>33</v>
+      </c>
+      <c r="F16">
         <v>20</v>
       </c>
-      <c r="G12" s="1">
-        <v>1.46</v>
-      </c>
-      <c r="H12">
-        <v>29.2</v>
-      </c>
-      <c r="I12" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="J12">
-        <v>29.8</v>
-      </c>
-      <c r="K12" t="s">
-        <v>45</v>
-      </c>
-      <c r="L12">
-        <v>54999</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
-      <c r="A15" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-    </row>
-    <row r="16" spans="1:12">
-      <c r="A16" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D16" s="5" t="s">
+      <c r="G16" t="s">
+        <v>35</v>
+      </c>
+      <c r="H16">
+        <v>1.74</v>
+      </c>
+      <c r="I16" s="1">
+        <v>34.8</v>
+      </c>
+      <c r="J16">
+        <v>1.77</v>
+      </c>
+      <c r="K16" s="1">
+        <v>35.4</v>
+      </c>
+      <c r="L16" t="s">
         <v>50</v>
       </c>
-      <c r="E16" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="6" t="s">
+      <c r="M16">
+        <v>7780</v>
+      </c>
+      <c r="N16" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" s="3">
+        <v>46234</v>
+      </c>
+      <c r="B17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" t="s">
+        <v>33</v>
+      </c>
+      <c r="F17">
+        <v>18.52</v>
+      </c>
+      <c r="G17" t="s">
+        <v>35</v>
+      </c>
+      <c r="H17">
+        <v>1.74</v>
+      </c>
+      <c r="I17" s="1">
+        <v>32.22</v>
+      </c>
+      <c r="J17">
+        <v>1.77</v>
+      </c>
+      <c r="K17" s="1">
+        <v>32.78</v>
+      </c>
+      <c r="L17" t="s">
+        <v>51</v>
+      </c>
+      <c r="M17">
+        <v>300924</v>
+      </c>
+      <c r="N17" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" s="3">
+        <v>46234</v>
+      </c>
+      <c r="B18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" t="s">
+        <v>33</v>
+      </c>
+      <c r="F18">
+        <v>61.01</v>
+      </c>
+      <c r="G18" t="s">
+        <v>35</v>
+      </c>
+      <c r="H18">
+        <v>1.74</v>
+      </c>
+      <c r="I18" s="1">
+        <v>106.16</v>
+      </c>
+      <c r="J18">
+        <v>1.77</v>
+      </c>
+      <c r="K18" s="1">
+        <v>107.99</v>
+      </c>
+      <c r="L18" t="s">
+        <v>52</v>
+      </c>
+      <c r="M18">
+        <v>193117</v>
+      </c>
+      <c r="N18" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" s="3">
+        <v>46234</v>
+      </c>
+      <c r="B19" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="7">
-        <v>457.72</v>
-      </c>
-      <c r="C17" s="7">
-        <v>9</v>
-      </c>
-      <c r="D17" s="8">
-        <v>1.5129</v>
-      </c>
-      <c r="E17" s="7">
-        <v>692.47</v>
-      </c>
-      <c r="F17" s="7">
-        <v>706.2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="6" t="s">
+      <c r="E19" t="s">
+        <v>33</v>
+      </c>
+      <c r="F19">
+        <v>56</v>
+      </c>
+      <c r="G19" t="s">
+        <v>35</v>
+      </c>
+      <c r="H19">
+        <v>1.74</v>
+      </c>
+      <c r="I19" s="1">
+        <v>97.44</v>
+      </c>
+      <c r="J19">
+        <v>1.77</v>
+      </c>
+      <c r="K19" s="1">
+        <v>99.12</v>
+      </c>
+      <c r="L19" t="s">
+        <v>53</v>
+      </c>
+      <c r="M19">
+        <v>278902</v>
+      </c>
+      <c r="N19" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" s="3">
+        <v>46234</v>
+      </c>
+      <c r="B20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E20" t="s">
+        <v>33</v>
+      </c>
+      <c r="F20">
+        <v>43.26</v>
+      </c>
+      <c r="G20" t="s">
+        <v>35</v>
+      </c>
+      <c r="H20">
+        <v>1.74</v>
+      </c>
+      <c r="I20" s="1">
+        <v>75.27</v>
+      </c>
+      <c r="J20">
+        <v>1.77</v>
+      </c>
+      <c r="K20" s="1">
+        <v>76.56999999999999</v>
+      </c>
+      <c r="L20" t="s">
+        <v>54</v>
+      </c>
+      <c r="M20">
+        <v>197492</v>
+      </c>
+      <c r="N20" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" s="3">
+        <v>46234</v>
+      </c>
+      <c r="B21" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" t="s">
+        <v>31</v>
+      </c>
+      <c r="E21" t="s">
+        <v>33</v>
+      </c>
+      <c r="F21">
+        <v>38.58</v>
+      </c>
+      <c r="G21" t="s">
+        <v>35</v>
+      </c>
+      <c r="H21">
+        <v>1.74</v>
+      </c>
+      <c r="I21" s="1">
+        <v>67.13</v>
+      </c>
+      <c r="J21">
+        <v>1.77</v>
+      </c>
+      <c r="K21" s="1">
+        <v>68.29000000000001</v>
+      </c>
+      <c r="L21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M21">
+        <v>7874</v>
+      </c>
+      <c r="N21" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" s="3">
+        <v>46234</v>
+      </c>
+      <c r="B22" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" t="s">
+        <v>25</v>
+      </c>
+      <c r="E22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F22">
+        <v>64</v>
+      </c>
+      <c r="G22" t="s">
+        <v>35</v>
+      </c>
+      <c r="H22">
+        <v>1.74</v>
+      </c>
+      <c r="I22" s="1">
+        <v>111.36</v>
+      </c>
+      <c r="J22">
+        <v>1.77</v>
+      </c>
+      <c r="K22" s="1">
+        <v>113.28</v>
+      </c>
+      <c r="L22" t="s">
+        <v>55</v>
+      </c>
+      <c r="M22">
+        <v>107791</v>
+      </c>
+      <c r="N22" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="7">
+        <v>831.9400000000001</v>
+      </c>
+      <c r="C27" s="7">
+        <v>19</v>
+      </c>
+      <c r="D27" s="8">
+        <v>1.6951</v>
+      </c>
+      <c r="E27" s="7">
+        <v>1410.22</v>
+      </c>
+      <c r="F27" s="7">
+        <v>1435.19</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="7">
-        <v>20</v>
-      </c>
-      <c r="C18" s="7">
-        <v>1</v>
-      </c>
-      <c r="D18" s="8">
-        <v>1.46</v>
-      </c>
-      <c r="E18" s="7">
-        <v>29.2</v>
-      </c>
-      <c r="F18" s="7">
-        <v>29.8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B19" s="7">
-        <v>9.5</v>
-      </c>
-      <c r="C19" s="7">
-        <v>1</v>
-      </c>
-      <c r="D19" s="8">
-        <v>1.7895</v>
-      </c>
-      <c r="E19" s="7">
-        <v>17</v>
-      </c>
-      <c r="F19" s="7">
-        <v>17.29</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="B20" s="10">
-        <v>487.22</v>
-      </c>
-      <c r="C20" s="10">
-        <v>11</v>
-      </c>
-      <c r="D20" s="8"/>
-      <c r="E20" s="10">
-        <v>738.67</v>
-      </c>
-      <c r="F20" s="10">
-        <v>753.29</v>
+      <c r="B28" s="7">
+        <v>68</v>
+      </c>
+      <c r="C28" s="7">
+        <v>2</v>
+      </c>
+      <c r="D28" s="8">
+        <v>1.5156</v>
+      </c>
+      <c r="E28" s="7">
+        <v>103.06</v>
+      </c>
+      <c r="F28" s="7">
+        <v>105.1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="B29" s="10">
+        <v>899.9400000000001</v>
+      </c>
+      <c r="C29" s="10">
+        <v>21</v>
+      </c>
+      <c r="D29" s="8"/>
+      <c r="E29" s="10">
+        <v>1513.28</v>
+      </c>
+      <c r="F29" s="10">
+        <v>1540.29</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП КОМПЛЕКС ЗА ДЕТСКО ХРАНЕНЕ/ОП КОМПЛЕКС ЗА ДЕТСКО ХРАНЕНЕ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП КОМПЛЕКС ЗА ДЕТСКО ХРАНЕНЕ/ОП КОМПЛЕКС ЗА ДЕТСКО ХРАНЕНЕ.xlsx
@@ -272,7 +272,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -1692,7 +1692,7 @@
         <v>19</v>
       </c>
       <c r="D27" s="8">
-        <v>1.6951</v>
+        <v>1.695098</v>
       </c>
       <c r="E27" s="7">
         <v>1410.22</v>
@@ -1712,7 +1712,7 @@
         <v>2</v>
       </c>
       <c r="D28" s="8">
-        <v>1.5156</v>
+        <v>1.515588</v>
       </c>
       <c r="E28" s="7">
         <v>103.06</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП КОМПЛЕКС ЗА ДЕТСКО ХРАНЕНЕ/ОП КОМПЛЕКС ЗА ДЕТСКО ХРАНЕНЕ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП КОМПЛЕКС ЗА ДЕТСКО ХРАНЕНЕ/ОП КОМПЛЕКС ЗА ДЕТСКО ХРАНЕНЕ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="84">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -664,7 +667,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N29"/>
+  <dimension ref="A1:O29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -677,13 +680,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -726,934 +729,1000 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" s="3">
         <v>46219</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F2">
         <v>46</v>
       </c>
       <c r="G2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H2">
+        <v>1.499</v>
+      </c>
+      <c r="I2" s="1">
         <v>1.58</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>72.68000000000001</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>1.61</v>
       </c>
-      <c r="K2" s="1">
+      <c r="L2" s="1">
         <v>74.06</v>
       </c>
-      <c r="L2" t="s">
-        <v>36</v>
-      </c>
-      <c r="M2">
+      <c r="M2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N2">
         <v>106588</v>
       </c>
-      <c r="N2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="O2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" s="3">
         <v>46220</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F3">
         <v>40</v>
       </c>
       <c r="G3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H3">
+        <v>1.499</v>
+      </c>
+      <c r="I3" s="1">
         <v>1.6</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>64</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>1.63</v>
       </c>
-      <c r="K3" s="1">
+      <c r="L3" s="1">
         <v>65.2</v>
       </c>
-      <c r="L3" t="s">
-        <v>37</v>
-      </c>
-      <c r="M3">
+      <c r="M3" t="s">
+        <v>38</v>
+      </c>
+      <c r="N3">
         <v>196470</v>
       </c>
-      <c r="N3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="O3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" s="3">
         <v>46223</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F4">
         <v>50</v>
       </c>
       <c r="G4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H4">
+        <v>1.546</v>
+      </c>
+      <c r="I4" s="1">
         <v>1.65</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>82.5</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>1.68</v>
       </c>
-      <c r="K4" s="1">
+      <c r="L4" s="1">
         <v>84</v>
       </c>
-      <c r="L4" t="s">
-        <v>38</v>
-      </c>
-      <c r="M4">
+      <c r="M4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N4">
         <v>192174</v>
       </c>
-      <c r="N4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="O4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" s="3">
         <v>46223</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F5">
-        <v>61.21</v>
+        <v>61.208</v>
       </c>
       <c r="G5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H5">
+        <v>1.546</v>
+      </c>
+      <c r="I5" s="1">
         <v>1.65</v>
       </c>
-      <c r="I5" s="1">
-        <v>101</v>
-      </c>
       <c r="J5">
+        <v>100.9932</v>
+      </c>
+      <c r="K5" s="1">
         <v>1.68</v>
       </c>
-      <c r="K5" s="1">
-        <v>102.83</v>
-      </c>
-      <c r="L5" t="s">
-        <v>39</v>
-      </c>
-      <c r="M5">
+      <c r="L5" s="1">
+        <v>102.82944</v>
+      </c>
+      <c r="M5" t="s">
+        <v>40</v>
+      </c>
+      <c r="N5">
         <v>292456</v>
       </c>
-      <c r="N5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="O5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" s="3">
         <v>46223</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F6">
-        <v>34.17</v>
+        <v>34.173</v>
       </c>
       <c r="G6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H6">
+        <v>1.546</v>
+      </c>
+      <c r="I6" s="1">
         <v>1.65</v>
       </c>
-      <c r="I6" s="1">
-        <v>56.38</v>
-      </c>
       <c r="J6">
+        <v>56.38545</v>
+      </c>
+      <c r="K6" s="1">
         <v>1.68</v>
       </c>
-      <c r="K6" s="1">
-        <v>57.41</v>
-      </c>
-      <c r="L6" t="s">
-        <v>40</v>
-      </c>
-      <c r="M6">
+      <c r="L6" s="1">
+        <v>57.41064</v>
+      </c>
+      <c r="M6" t="s">
+        <v>41</v>
+      </c>
+      <c r="N6">
         <v>300120</v>
       </c>
-      <c r="N6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="O6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" s="3">
         <v>46225</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F7">
-        <v>42.02</v>
+        <v>42.018</v>
       </c>
       <c r="G7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H7">
+        <v>1.588</v>
+      </c>
+      <c r="I7" s="1">
         <v>1.66</v>
       </c>
-      <c r="I7" s="1">
-        <v>69.75</v>
-      </c>
       <c r="J7">
+        <v>69.74988</v>
+      </c>
+      <c r="K7" s="1">
         <v>1.69</v>
       </c>
-      <c r="K7" s="1">
-        <v>71.01000000000001</v>
-      </c>
-      <c r="L7" t="s">
-        <v>41</v>
-      </c>
-      <c r="M7">
+      <c r="L7" s="1">
+        <v>71.01042</v>
+      </c>
+      <c r="M7" t="s">
+        <v>42</v>
+      </c>
+      <c r="N7">
         <v>106052</v>
       </c>
-      <c r="N7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="O7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" s="3">
         <v>46225</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F8">
         <v>30</v>
       </c>
       <c r="G8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H8">
+        <v>1.401</v>
+      </c>
+      <c r="I8" s="1">
         <v>1.51</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8">
         <v>45.3</v>
       </c>
-      <c r="J8">
+      <c r="K8" s="1">
         <v>1.54</v>
       </c>
-      <c r="K8" s="1">
+      <c r="L8" s="1">
         <v>46.2</v>
       </c>
-      <c r="L8" t="s">
-        <v>42</v>
-      </c>
-      <c r="M8">
+      <c r="M8" t="s">
+        <v>43</v>
+      </c>
+      <c r="N8">
         <v>55280</v>
       </c>
-      <c r="N8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="O8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" s="3">
         <v>46226</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F9">
         <v>40</v>
       </c>
       <c r="G9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H9">
+        <v>1.588</v>
+      </c>
+      <c r="I9" s="1">
         <v>1.67</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9">
         <v>66.8</v>
       </c>
-      <c r="J9">
+      <c r="K9" s="1">
         <v>1.7</v>
       </c>
-      <c r="K9" s="1">
+      <c r="L9" s="1">
         <v>68</v>
       </c>
-      <c r="L9" t="s">
-        <v>43</v>
-      </c>
-      <c r="M9">
+      <c r="M9" t="s">
+        <v>44</v>
+      </c>
+      <c r="N9">
         <v>7200</v>
       </c>
-      <c r="N9" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="O9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" s="3">
         <v>46227</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F10">
         <v>40</v>
       </c>
       <c r="G10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H10">
+        <v>1.619</v>
+      </c>
+      <c r="I10" s="1">
         <v>1.69</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10">
         <v>67.59999999999999</v>
       </c>
-      <c r="J10">
+      <c r="K10" s="1">
         <v>1.72</v>
       </c>
-      <c r="K10" s="1">
+      <c r="L10" s="1">
         <v>68.8</v>
       </c>
-      <c r="L10" t="s">
-        <v>44</v>
-      </c>
-      <c r="M10">
+      <c r="M10" t="s">
+        <v>45</v>
+      </c>
+      <c r="N10">
         <v>196940</v>
       </c>
-      <c r="N10" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="O10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" s="3">
         <v>46230</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F11">
         <v>50</v>
       </c>
       <c r="G11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H11">
+        <v>1.619</v>
+      </c>
+      <c r="I11" s="1">
         <v>1.72</v>
       </c>
-      <c r="I11" s="1">
+      <c r="J11">
         <v>86</v>
       </c>
-      <c r="J11">
+      <c r="K11" s="1">
         <v>1.75</v>
       </c>
-      <c r="K11" s="1">
+      <c r="L11" s="1">
         <v>87.5</v>
       </c>
-      <c r="L11" t="s">
-        <v>45</v>
-      </c>
-      <c r="M11">
+      <c r="M11" t="s">
+        <v>46</v>
+      </c>
+      <c r="N11">
         <v>192695</v>
       </c>
-      <c r="N11" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="O11" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" s="3">
         <v>46231</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F12">
         <v>40</v>
       </c>
       <c r="G12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H12">
+        <v>1.653</v>
+      </c>
+      <c r="I12" s="1">
         <v>1.72</v>
       </c>
-      <c r="I12" s="1">
+      <c r="J12">
         <v>68.8</v>
       </c>
-      <c r="J12">
+      <c r="K12" s="1">
         <v>1.75</v>
       </c>
-      <c r="K12" s="1">
+      <c r="L12" s="1">
         <v>70</v>
       </c>
-      <c r="L12" t="s">
-        <v>46</v>
-      </c>
-      <c r="M12">
+      <c r="M12" t="s">
+        <v>47</v>
+      </c>
+      <c r="N12">
         <v>7474</v>
       </c>
-      <c r="N12" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="O12" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" s="3">
         <v>46232</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F13">
-        <v>47.17</v>
+        <v>47.171</v>
       </c>
       <c r="G13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H13">
+        <v>1.674</v>
+      </c>
+      <c r="I13" s="1">
         <v>1.72</v>
       </c>
-      <c r="I13" s="1">
-        <v>81.13</v>
-      </c>
       <c r="J13">
+        <v>81.13412</v>
+      </c>
+      <c r="K13" s="1">
         <v>1.75</v>
       </c>
-      <c r="K13" s="1">
-        <v>82.55</v>
-      </c>
-      <c r="L13" t="s">
-        <v>47</v>
-      </c>
-      <c r="M13">
+      <c r="L13" s="1">
+        <v>82.54925</v>
+      </c>
+      <c r="M13" t="s">
+        <v>48</v>
+      </c>
+      <c r="N13">
         <v>300679</v>
       </c>
-      <c r="N13" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+      <c r="O13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14" s="3">
         <v>46233</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F14">
         <v>40</v>
       </c>
       <c r="G14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H14">
+        <v>1.674</v>
+      </c>
+      <c r="I14" s="1">
         <v>1.73</v>
       </c>
-      <c r="I14" s="1">
+      <c r="J14">
         <v>69.2</v>
       </c>
-      <c r="J14">
+      <c r="K14" s="1">
         <v>1.76</v>
       </c>
-      <c r="K14" s="1">
+      <c r="L14" s="1">
         <v>70.40000000000001</v>
       </c>
-      <c r="L14" t="s">
-        <v>48</v>
-      </c>
-      <c r="M14">
+      <c r="M14" t="s">
+        <v>49</v>
+      </c>
+      <c r="N14">
         <v>197370</v>
       </c>
-      <c r="N14" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+      <c r="O14" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="A15" s="3">
         <v>46234</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F15">
         <v>38</v>
       </c>
       <c r="G15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H15">
+        <v>1.459</v>
+      </c>
+      <c r="I15" s="1">
         <v>1.52</v>
       </c>
-      <c r="I15" s="1">
+      <c r="J15">
         <v>57.76</v>
       </c>
-      <c r="J15">
+      <c r="K15" s="1">
         <v>1.55</v>
       </c>
-      <c r="K15" s="1">
+      <c r="L15" s="1">
         <v>58.9</v>
       </c>
-      <c r="L15" t="s">
-        <v>49</v>
-      </c>
-      <c r="M15">
+      <c r="M15" t="s">
+        <v>50</v>
+      </c>
+      <c r="N15">
         <v>55436</v>
       </c>
-      <c r="N15" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+      <c r="O15" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
       <c r="A16" s="3">
         <v>46234</v>
       </c>
       <c r="B16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F16">
         <v>20</v>
       </c>
       <c r="G16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H16">
+        <v>1.689</v>
+      </c>
+      <c r="I16" s="1">
         <v>1.74</v>
       </c>
-      <c r="I16" s="1">
+      <c r="J16">
         <v>34.8</v>
       </c>
-      <c r="J16">
+      <c r="K16" s="1">
         <v>1.77</v>
       </c>
-      <c r="K16" s="1">
+      <c r="L16" s="1">
         <v>35.4</v>
       </c>
-      <c r="L16" t="s">
-        <v>50</v>
-      </c>
-      <c r="M16">
+      <c r="M16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N16">
         <v>7780</v>
       </c>
-      <c r="N16" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
+      <c r="O16" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
       <c r="A17" s="3">
         <v>46234</v>
       </c>
       <c r="B17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D17" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E17" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F17">
         <v>18.52</v>
       </c>
       <c r="G17" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H17">
+        <v>1.689</v>
+      </c>
+      <c r="I17" s="1">
         <v>1.74</v>
       </c>
-      <c r="I17" s="1">
-        <v>32.22</v>
-      </c>
       <c r="J17">
+        <v>32.2248</v>
+      </c>
+      <c r="K17" s="1">
         <v>1.77</v>
       </c>
-      <c r="K17" s="1">
-        <v>32.78</v>
-      </c>
-      <c r="L17" t="s">
-        <v>51</v>
-      </c>
-      <c r="M17">
+      <c r="L17" s="1">
+        <v>32.7804</v>
+      </c>
+      <c r="M17" t="s">
+        <v>52</v>
+      </c>
+      <c r="N17">
         <v>300924</v>
       </c>
-      <c r="N17" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
+      <c r="O17" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
       <c r="A18" s="3">
         <v>46234</v>
       </c>
       <c r="B18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F18">
-        <v>61.01</v>
+        <v>61.011</v>
       </c>
       <c r="G18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H18">
+        <v>1.689</v>
+      </c>
+      <c r="I18" s="1">
         <v>1.74</v>
       </c>
-      <c r="I18" s="1">
-        <v>106.16</v>
-      </c>
       <c r="J18">
+        <v>106.15914</v>
+      </c>
+      <c r="K18" s="1">
         <v>1.77</v>
       </c>
-      <c r="K18" s="1">
-        <v>107.99</v>
-      </c>
-      <c r="L18" t="s">
-        <v>52</v>
-      </c>
-      <c r="M18">
+      <c r="L18" s="1">
+        <v>107.98947</v>
+      </c>
+      <c r="M18" t="s">
+        <v>53</v>
+      </c>
+      <c r="N18">
         <v>193117</v>
       </c>
-      <c r="N18" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
+      <c r="O18" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
       <c r="A19" s="3">
         <v>46234</v>
       </c>
       <c r="B19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F19">
         <v>56</v>
       </c>
       <c r="G19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H19">
+        <v>1.689</v>
+      </c>
+      <c r="I19" s="1">
         <v>1.74</v>
       </c>
-      <c r="I19" s="1">
+      <c r="J19">
         <v>97.44</v>
       </c>
-      <c r="J19">
+      <c r="K19" s="1">
         <v>1.77</v>
       </c>
-      <c r="K19" s="1">
+      <c r="L19" s="1">
         <v>99.12</v>
       </c>
-      <c r="L19" t="s">
-        <v>53</v>
-      </c>
-      <c r="M19">
+      <c r="M19" t="s">
+        <v>54</v>
+      </c>
+      <c r="N19">
         <v>278902</v>
       </c>
-      <c r="N19" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
+      <c r="O19" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
       <c r="A20" s="3">
         <v>46234</v>
       </c>
       <c r="B20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F20">
         <v>43.26</v>
       </c>
       <c r="G20" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H20">
+        <v>1.689</v>
+      </c>
+      <c r="I20" s="1">
         <v>1.74</v>
       </c>
-      <c r="I20" s="1">
-        <v>75.27</v>
-      </c>
       <c r="J20">
+        <v>75.2724</v>
+      </c>
+      <c r="K20" s="1">
         <v>1.77</v>
       </c>
-      <c r="K20" s="1">
-        <v>76.56999999999999</v>
-      </c>
-      <c r="L20" t="s">
-        <v>54</v>
-      </c>
-      <c r="M20">
+      <c r="L20" s="1">
+        <v>76.5702</v>
+      </c>
+      <c r="M20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N20">
         <v>197492</v>
       </c>
-      <c r="N20" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
+      <c r="O20" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
       <c r="A21" s="3">
         <v>46234</v>
       </c>
       <c r="B21" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C21" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D21" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E21" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F21">
-        <v>38.58</v>
+        <v>38.582</v>
       </c>
       <c r="G21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H21">
+        <v>1.689</v>
+      </c>
+      <c r="I21" s="1">
         <v>1.74</v>
       </c>
-      <c r="I21" s="1">
-        <v>67.13</v>
-      </c>
       <c r="J21">
+        <v>67.13267999999999</v>
+      </c>
+      <c r="K21" s="1">
         <v>1.77</v>
       </c>
-      <c r="K21" s="1">
-        <v>68.29000000000001</v>
-      </c>
-      <c r="L21" t="s">
-        <v>39</v>
-      </c>
-      <c r="M21">
+      <c r="L21" s="1">
+        <v>68.29013999999999</v>
+      </c>
+      <c r="M21" t="s">
+        <v>40</v>
+      </c>
+      <c r="N21">
         <v>7874</v>
       </c>
-      <c r="N21" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14">
+      <c r="O21" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
       <c r="A22" s="3">
         <v>46234</v>
       </c>
       <c r="B22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D22" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E22" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F22">
         <v>64</v>
       </c>
       <c r="G22" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H22">
+        <v>1.689</v>
+      </c>
+      <c r="I22" s="1">
         <v>1.74</v>
       </c>
-      <c r="I22" s="1">
+      <c r="J22">
         <v>111.36</v>
       </c>
-      <c r="J22">
+      <c r="K22" s="1">
         <v>1.77</v>
       </c>
-      <c r="K22" s="1">
+      <c r="L22" s="1">
         <v>113.28</v>
       </c>
-      <c r="L22" t="s">
-        <v>55</v>
-      </c>
-      <c r="M22">
+      <c r="M22" t="s">
+        <v>56</v>
+      </c>
+      <c r="N22">
         <v>107791</v>
       </c>
-      <c r="N22" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14">
+      <c r="O22" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15">
       <c r="A25" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
@@ -1661,49 +1730,49 @@
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
     </row>
-    <row r="26" spans="1:14">
+    <row r="26" spans="1:15">
       <c r="A26" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15">
       <c r="A27" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27" s="7">
-        <v>831.9400000000001</v>
+        <v>831.943</v>
       </c>
       <c r="C27" s="7">
         <v>19</v>
       </c>
       <c r="D27" s="8">
-        <v>1.695098</v>
+        <v>1.695106</v>
       </c>
       <c r="E27" s="7">
-        <v>1410.22</v>
+        <v>1410.23</v>
       </c>
       <c r="F27" s="7">
         <v>1435.19</v>
       </c>
     </row>
-    <row r="28" spans="1:14">
+    <row r="28" spans="1:15">
       <c r="A28" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B28" s="7">
         <v>68</v>
@@ -1721,19 +1790,19 @@
         <v>105.1</v>
       </c>
     </row>
-    <row r="29" spans="1:14">
+    <row r="29" spans="1:15">
       <c r="A29" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B29" s="10">
-        <v>899.9400000000001</v>
+        <v>899.943</v>
       </c>
       <c r="C29" s="10">
         <v>21</v>
       </c>
       <c r="D29" s="8"/>
       <c r="E29" s="10">
-        <v>1513.28</v>
+        <v>1513.29</v>
       </c>
       <c r="F29" s="10">
         <v>1540.29</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП КОМПЛЕКС ЗА ДЕТСКО ХРАНЕНЕ/ОП КОМПЛЕКС ЗА ДЕТСКО ХРАНЕНЕ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП КОМПЛЕКС ЗА ДЕТСКО ХРАНЕНЕ/ОП КОМПЛЕКС ЗА ДЕТСКО ХРАНЕНЕ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="83">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -273,9 +270,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -369,10 +366,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -667,7 +664,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O29"/>
+  <dimension ref="A1:N29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -680,13 +677,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -729,1000 +726,934 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15">
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46219</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F2">
         <v>46</v>
       </c>
       <c r="G2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H2">
+        <v>1.58</v>
+      </c>
+      <c r="I2" s="1">
+        <v>72.68000000000001</v>
+      </c>
+      <c r="J2">
+        <v>1.61</v>
+      </c>
+      <c r="K2" s="1">
+        <v>74.06</v>
+      </c>
+      <c r="L2" t="s">
         <v>36</v>
       </c>
-      <c r="H2">
-        <v>1.499</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.58</v>
-      </c>
-      <c r="J2">
-        <v>72.68000000000001</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1.61</v>
-      </c>
-      <c r="L2" s="1">
-        <v>74.06</v>
-      </c>
-      <c r="M2" t="s">
-        <v>37</v>
-      </c>
-      <c r="N2">
+      <c r="M2">
         <v>106588</v>
       </c>
-      <c r="O2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="N2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>46220</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F3">
         <v>40</v>
       </c>
       <c r="G3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H3">
-        <v>1.499</v>
+        <v>1.6</v>
       </c>
       <c r="I3" s="1">
-        <v>1.6</v>
+        <v>64</v>
       </c>
       <c r="J3">
-        <v>64</v>
+        <v>1.63</v>
       </c>
       <c r="K3" s="1">
-        <v>1.63</v>
-      </c>
-      <c r="L3" s="1">
         <v>65.2</v>
       </c>
-      <c r="M3" t="s">
-        <v>38</v>
-      </c>
-      <c r="N3">
+      <c r="L3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M3">
         <v>196470</v>
       </c>
-      <c r="O3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="N3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
         <v>46223</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F4">
         <v>50</v>
       </c>
       <c r="G4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H4">
-        <v>1.546</v>
+        <v>1.65</v>
       </c>
       <c r="I4" s="1">
-        <v>1.65</v>
+        <v>82.5</v>
       </c>
       <c r="J4">
-        <v>82.5</v>
+        <v>1.68</v>
       </c>
       <c r="K4" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L4" s="1">
         <v>84</v>
       </c>
-      <c r="M4" t="s">
-        <v>39</v>
-      </c>
-      <c r="N4">
+      <c r="L4" t="s">
+        <v>38</v>
+      </c>
+      <c r="M4">
         <v>192174</v>
       </c>
-      <c r="O4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="N4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="3">
         <v>46223</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F5">
         <v>61.208</v>
       </c>
       <c r="G5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H5">
-        <v>1.546</v>
+        <v>1.65</v>
       </c>
       <c r="I5" s="1">
-        <v>1.65</v>
+        <v>100.993</v>
       </c>
       <c r="J5">
-        <v>100.9932</v>
+        <v>1.68</v>
       </c>
       <c r="K5" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L5" s="1">
-        <v>102.82944</v>
-      </c>
-      <c r="M5" t="s">
-        <v>40</v>
-      </c>
-      <c r="N5">
+        <v>102.829</v>
+      </c>
+      <c r="L5" t="s">
+        <v>39</v>
+      </c>
+      <c r="M5">
         <v>292456</v>
       </c>
-      <c r="O5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="N5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="3">
         <v>46223</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F6">
         <v>34.173</v>
       </c>
       <c r="G6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H6">
-        <v>1.546</v>
+        <v>1.65</v>
       </c>
       <c r="I6" s="1">
-        <v>1.65</v>
+        <v>56.385</v>
       </c>
       <c r="J6">
-        <v>56.38545</v>
+        <v>1.68</v>
       </c>
       <c r="K6" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L6" s="1">
-        <v>57.41064</v>
-      </c>
-      <c r="M6" t="s">
-        <v>41</v>
-      </c>
-      <c r="N6">
+        <v>57.411</v>
+      </c>
+      <c r="L6" t="s">
+        <v>40</v>
+      </c>
+      <c r="M6">
         <v>300120</v>
       </c>
-      <c r="O6" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="N6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="3">
         <v>46225</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F7">
         <v>42.018</v>
       </c>
       <c r="G7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H7">
-        <v>1.588</v>
+        <v>1.66</v>
       </c>
       <c r="I7" s="1">
-        <v>1.66</v>
+        <v>69.75</v>
       </c>
       <c r="J7">
-        <v>69.74988</v>
+        <v>1.69</v>
       </c>
       <c r="K7" s="1">
-        <v>1.69</v>
-      </c>
-      <c r="L7" s="1">
-        <v>71.01042</v>
-      </c>
-      <c r="M7" t="s">
-        <v>42</v>
-      </c>
-      <c r="N7">
+        <v>71.01000000000001</v>
+      </c>
+      <c r="L7" t="s">
+        <v>41</v>
+      </c>
+      <c r="M7">
         <v>106052</v>
       </c>
-      <c r="O7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+      <c r="N7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="3">
         <v>46225</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F8">
         <v>30</v>
       </c>
       <c r="G8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H8">
-        <v>1.401</v>
+        <v>1.51</v>
       </c>
       <c r="I8" s="1">
-        <v>1.51</v>
+        <v>45.3</v>
       </c>
       <c r="J8">
-        <v>45.3</v>
+        <v>1.54</v>
       </c>
       <c r="K8" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L8" s="1">
         <v>46.2</v>
       </c>
-      <c r="M8" t="s">
-        <v>43</v>
-      </c>
-      <c r="N8">
+      <c r="L8" t="s">
+        <v>42</v>
+      </c>
+      <c r="M8">
         <v>55280</v>
       </c>
-      <c r="O8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+      <c r="N8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" s="3">
         <v>46226</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F9">
         <v>40</v>
       </c>
       <c r="G9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H9">
-        <v>1.588</v>
+        <v>1.67</v>
       </c>
       <c r="I9" s="1">
-        <v>1.67</v>
+        <v>66.8</v>
       </c>
       <c r="J9">
-        <v>66.8</v>
+        <v>1.7</v>
       </c>
       <c r="K9" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="L9" s="1">
         <v>68</v>
       </c>
-      <c r="M9" t="s">
-        <v>44</v>
-      </c>
-      <c r="N9">
+      <c r="L9" t="s">
+        <v>43</v>
+      </c>
+      <c r="M9">
         <v>7200</v>
       </c>
-      <c r="O9" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+      <c r="N9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="3">
         <v>46227</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F10">
         <v>40</v>
       </c>
       <c r="G10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H10">
-        <v>1.619</v>
+        <v>1.69</v>
       </c>
       <c r="I10" s="1">
-        <v>1.69</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="J10">
-        <v>67.59999999999999</v>
+        <v>1.72</v>
       </c>
       <c r="K10" s="1">
-        <v>1.72</v>
-      </c>
-      <c r="L10" s="1">
         <v>68.8</v>
       </c>
-      <c r="M10" t="s">
-        <v>45</v>
-      </c>
-      <c r="N10">
+      <c r="L10" t="s">
+        <v>44</v>
+      </c>
+      <c r="M10">
         <v>196940</v>
       </c>
-      <c r="O10" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+      <c r="N10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="3">
         <v>46230</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F11">
         <v>50</v>
       </c>
       <c r="G11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H11">
-        <v>1.619</v>
+        <v>1.72</v>
       </c>
       <c r="I11" s="1">
-        <v>1.72</v>
+        <v>86</v>
       </c>
       <c r="J11">
-        <v>86</v>
+        <v>1.75</v>
       </c>
       <c r="K11" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L11" s="1">
         <v>87.5</v>
       </c>
-      <c r="M11" t="s">
-        <v>46</v>
-      </c>
-      <c r="N11">
+      <c r="L11" t="s">
+        <v>45</v>
+      </c>
+      <c r="M11">
         <v>192695</v>
       </c>
-      <c r="O11" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+      <c r="N11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="3">
         <v>46231</v>
       </c>
       <c r="B12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F12">
         <v>40</v>
       </c>
       <c r="G12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H12">
-        <v>1.653</v>
+        <v>1.72</v>
       </c>
       <c r="I12" s="1">
-        <v>1.72</v>
+        <v>68.8</v>
       </c>
       <c r="J12">
-        <v>68.8</v>
+        <v>1.75</v>
       </c>
       <c r="K12" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L12" s="1">
         <v>70</v>
       </c>
-      <c r="M12" t="s">
-        <v>47</v>
-      </c>
-      <c r="N12">
+      <c r="L12" t="s">
+        <v>46</v>
+      </c>
+      <c r="M12">
         <v>7474</v>
       </c>
-      <c r="O12" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+      <c r="N12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" s="3">
         <v>46232</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F13">
         <v>47.171</v>
       </c>
       <c r="G13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H13">
-        <v>1.674</v>
+        <v>1.72</v>
       </c>
       <c r="I13" s="1">
-        <v>1.72</v>
+        <v>81.134</v>
       </c>
       <c r="J13">
-        <v>81.13412</v>
+        <v>1.75</v>
       </c>
       <c r="K13" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L13" s="1">
-        <v>82.54925</v>
-      </c>
-      <c r="M13" t="s">
-        <v>48</v>
-      </c>
-      <c r="N13">
+        <v>82.54900000000001</v>
+      </c>
+      <c r="L13" t="s">
+        <v>47</v>
+      </c>
+      <c r="M13">
         <v>300679</v>
       </c>
-      <c r="O13" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+      <c r="N13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" s="3">
         <v>46233</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F14">
         <v>40</v>
       </c>
       <c r="G14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H14">
-        <v>1.674</v>
+        <v>1.73</v>
       </c>
       <c r="I14" s="1">
-        <v>1.73</v>
+        <v>69.2</v>
       </c>
       <c r="J14">
-        <v>69.2</v>
+        <v>1.76</v>
       </c>
       <c r="K14" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L14" s="1">
         <v>70.40000000000001</v>
       </c>
-      <c r="M14" t="s">
-        <v>49</v>
-      </c>
-      <c r="N14">
+      <c r="L14" t="s">
+        <v>48</v>
+      </c>
+      <c r="M14">
         <v>197370</v>
       </c>
-      <c r="O14" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+      <c r="N14" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" s="3">
         <v>46234</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F15">
         <v>38</v>
       </c>
       <c r="G15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H15">
-        <v>1.459</v>
+        <v>1.52</v>
       </c>
       <c r="I15" s="1">
-        <v>1.52</v>
+        <v>57.76</v>
       </c>
       <c r="J15">
-        <v>57.76</v>
+        <v>1.55</v>
       </c>
       <c r="K15" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L15" s="1">
         <v>58.9</v>
       </c>
-      <c r="M15" t="s">
-        <v>50</v>
-      </c>
-      <c r="N15">
+      <c r="L15" t="s">
+        <v>49</v>
+      </c>
+      <c r="M15">
         <v>55436</v>
       </c>
-      <c r="O15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
+      <c r="N15" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" s="3">
         <v>46234</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F16">
         <v>20</v>
       </c>
       <c r="G16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H16">
-        <v>1.689</v>
+        <v>1.74</v>
       </c>
       <c r="I16" s="1">
-        <v>1.74</v>
+        <v>34.8</v>
       </c>
       <c r="J16">
-        <v>34.8</v>
+        <v>1.77</v>
       </c>
       <c r="K16" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L16" s="1">
         <v>35.4</v>
       </c>
-      <c r="M16" t="s">
-        <v>51</v>
-      </c>
-      <c r="N16">
+      <c r="L16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M16">
         <v>7780</v>
       </c>
-      <c r="O16" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15">
+      <c r="N16" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" s="3">
         <v>46234</v>
       </c>
       <c r="B17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F17">
         <v>18.52</v>
       </c>
       <c r="G17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H17">
-        <v>1.689</v>
+        <v>1.74</v>
       </c>
       <c r="I17" s="1">
-        <v>1.74</v>
+        <v>32.225</v>
       </c>
       <c r="J17">
-        <v>32.2248</v>
+        <v>1.77</v>
       </c>
       <c r="K17" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L17" s="1">
-        <v>32.7804</v>
-      </c>
-      <c r="M17" t="s">
-        <v>52</v>
-      </c>
-      <c r="N17">
+        <v>32.78</v>
+      </c>
+      <c r="L17" t="s">
+        <v>51</v>
+      </c>
+      <c r="M17">
         <v>300924</v>
       </c>
-      <c r="O17" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15">
+      <c r="N17" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" s="3">
         <v>46234</v>
       </c>
       <c r="B18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F18">
         <v>61.011</v>
       </c>
       <c r="G18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H18">
-        <v>1.689</v>
+        <v>1.74</v>
       </c>
       <c r="I18" s="1">
-        <v>1.74</v>
+        <v>106.159</v>
       </c>
       <c r="J18">
-        <v>106.15914</v>
+        <v>1.77</v>
       </c>
       <c r="K18" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L18" s="1">
-        <v>107.98947</v>
-      </c>
-      <c r="M18" t="s">
-        <v>53</v>
-      </c>
-      <c r="N18">
+        <v>107.989</v>
+      </c>
+      <c r="L18" t="s">
+        <v>52</v>
+      </c>
+      <c r="M18">
         <v>193117</v>
       </c>
-      <c r="O18" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15">
+      <c r="N18" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" s="3">
         <v>46234</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F19">
         <v>56</v>
       </c>
       <c r="G19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H19">
-        <v>1.689</v>
+        <v>1.74</v>
       </c>
       <c r="I19" s="1">
-        <v>1.74</v>
+        <v>97.44</v>
       </c>
       <c r="J19">
-        <v>97.44</v>
+        <v>1.77</v>
       </c>
       <c r="K19" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L19" s="1">
         <v>99.12</v>
       </c>
-      <c r="M19" t="s">
-        <v>54</v>
-      </c>
-      <c r="N19">
+      <c r="L19" t="s">
+        <v>53</v>
+      </c>
+      <c r="M19">
         <v>278902</v>
       </c>
-      <c r="O19" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15">
+      <c r="N19" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" s="3">
         <v>46234</v>
       </c>
       <c r="B20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F20">
         <v>43.26</v>
       </c>
       <c r="G20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H20">
-        <v>1.689</v>
+        <v>1.74</v>
       </c>
       <c r="I20" s="1">
-        <v>1.74</v>
+        <v>75.27200000000001</v>
       </c>
       <c r="J20">
-        <v>75.2724</v>
+        <v>1.77</v>
       </c>
       <c r="K20" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L20" s="1">
-        <v>76.5702</v>
-      </c>
-      <c r="M20" t="s">
-        <v>55</v>
-      </c>
-      <c r="N20">
+        <v>76.56999999999999</v>
+      </c>
+      <c r="L20" t="s">
+        <v>54</v>
+      </c>
+      <c r="M20">
         <v>197492</v>
       </c>
-      <c r="O20" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15">
+      <c r="N20" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" s="3">
         <v>46234</v>
       </c>
       <c r="B21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F21">
         <v>38.582</v>
       </c>
       <c r="G21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H21">
-        <v>1.689</v>
+        <v>1.74</v>
       </c>
       <c r="I21" s="1">
-        <v>1.74</v>
+        <v>67.133</v>
       </c>
       <c r="J21">
-        <v>67.13267999999999</v>
+        <v>1.77</v>
       </c>
       <c r="K21" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L21" s="1">
-        <v>68.29013999999999</v>
-      </c>
-      <c r="M21" t="s">
-        <v>40</v>
-      </c>
-      <c r="N21">
+        <v>68.29000000000001</v>
+      </c>
+      <c r="L21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M21">
         <v>7874</v>
       </c>
-      <c r="O21" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15">
+      <c r="N21" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" s="3">
         <v>46234</v>
       </c>
       <c r="B22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F22">
         <v>64</v>
       </c>
       <c r="G22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H22">
-        <v>1.689</v>
+        <v>1.74</v>
       </c>
       <c r="I22" s="1">
-        <v>1.74</v>
+        <v>111.36</v>
       </c>
       <c r="J22">
-        <v>111.36</v>
+        <v>1.77</v>
       </c>
       <c r="K22" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L22" s="1">
         <v>113.28</v>
       </c>
-      <c r="M22" t="s">
-        <v>56</v>
-      </c>
-      <c r="N22">
+      <c r="L22" t="s">
+        <v>55</v>
+      </c>
+      <c r="M22">
         <v>107791</v>
       </c>
-      <c r="O22" t="s">
+      <c r="N22" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" s="4" t="s">
         <v>77</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15">
-      <c r="A25" s="4" t="s">
-        <v>78</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
@@ -1730,69 +1661,69 @@
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
     </row>
-    <row r="26" spans="1:15">
+    <row r="26" spans="1:14">
       <c r="A26" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B26" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="C26" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="D26" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="D26" s="5" t="s">
-        <v>82</v>
-      </c>
       <c r="E26" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
       <c r="A27" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B27" s="7">
         <v>831.943</v>
       </c>
-      <c r="C27" s="7">
+      <c r="C27" s="8">
         <v>19</v>
       </c>
       <c r="D27" s="8">
-        <v>1.695106</v>
-      </c>
-      <c r="E27" s="7">
-        <v>1410.23</v>
-      </c>
-      <c r="F27" s="7">
-        <v>1435.19</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15">
+        <v>1.695</v>
+      </c>
+      <c r="E27" s="8">
+        <v>1410.231</v>
+      </c>
+      <c r="F27" s="8">
+        <v>1435.188</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
       <c r="A28" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B28" s="7">
         <v>68</v>
       </c>
-      <c r="C28" s="7">
+      <c r="C28" s="8">
         <v>2</v>
       </c>
       <c r="D28" s="8">
-        <v>1.515588</v>
-      </c>
-      <c r="E28" s="7">
+        <v>1.516</v>
+      </c>
+      <c r="E28" s="8">
         <v>103.06</v>
       </c>
-      <c r="F28" s="7">
+      <c r="F28" s="8">
         <v>105.1</v>
       </c>
     </row>
-    <row r="29" spans="1:15">
+    <row r="29" spans="1:14">
       <c r="A29" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B29" s="10">
         <v>899.943</v>
@@ -1802,10 +1733,10 @@
       </c>
       <c r="D29" s="8"/>
       <c r="E29" s="10">
-        <v>1513.29</v>
+        <v>1513.291</v>
       </c>
       <c r="F29" s="10">
-        <v>1540.29</v>
+        <v>1540.288</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП КОМПЛЕКС ЗА ДЕТСКО ХРАНЕНЕ/ОП КОМПЛЕКС ЗА ДЕТСКО ХРАНЕНЕ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП КОМПЛЕКС ЗА ДЕТСКО ХРАНЕНЕ/ОП КОМПЛЕКС ЗА ДЕТСКО ХРАНЕНЕ.xlsx
@@ -768,10 +768,10 @@
         <v>36</v>
       </c>
       <c r="H2" s="1">
-        <v>1.657</v>
+        <v>1.77</v>
       </c>
       <c r="I2" s="1">
-        <v>66.28</v>
+        <v>70.8</v>
       </c>
       <c r="J2" s="1">
         <v>1.8</v>
@@ -812,10 +812,10 @@
         <v>36</v>
       </c>
       <c r="H3" s="1">
-        <v>1.657</v>
+        <v>1.77</v>
       </c>
       <c r="I3" s="1">
-        <v>82.867</v>
+        <v>88.518</v>
       </c>
       <c r="J3" s="1">
         <v>1.8</v>
@@ -856,10 +856,10 @@
         <v>36</v>
       </c>
       <c r="H4" s="1">
-        <v>1.677</v>
+        <v>1.77</v>
       </c>
       <c r="I4" s="1">
-        <v>109.005</v>
+        <v>115.05</v>
       </c>
       <c r="J4" s="1">
         <v>1.8</v>
@@ -900,10 +900,10 @@
         <v>36</v>
       </c>
       <c r="H5" s="1">
-        <v>1.677</v>
+        <v>1.79</v>
       </c>
       <c r="I5" s="1">
-        <v>67.08</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="J5" s="1">
         <v>1.82</v>
@@ -944,10 +944,10 @@
         <v>36</v>
       </c>
       <c r="H6" s="1">
-        <v>1.689</v>
+        <v>1.81</v>
       </c>
       <c r="I6" s="1">
-        <v>101.34</v>
+        <v>108.6</v>
       </c>
       <c r="J6" s="1">
         <v>1.84</v>
@@ -988,10 +988,10 @@
         <v>36</v>
       </c>
       <c r="H7" s="1">
-        <v>1.689</v>
+        <v>1.81</v>
       </c>
       <c r="I7" s="1">
-        <v>59.115</v>
+        <v>63.35</v>
       </c>
       <c r="J7" s="1">
         <v>1.84</v>
@@ -1032,10 +1032,10 @@
         <v>36</v>
       </c>
       <c r="H8" s="1">
-        <v>1.429</v>
+        <v>1.54</v>
       </c>
       <c r="I8" s="1">
-        <v>36.411</v>
+        <v>39.239</v>
       </c>
       <c r="J8" s="1">
         <v>1.57</v>
@@ -1076,10 +1076,10 @@
         <v>36</v>
       </c>
       <c r="H9" s="1">
-        <v>1.689</v>
+        <v>1.81</v>
       </c>
       <c r="I9" s="1">
-        <v>65.88800000000001</v>
+        <v>70.608</v>
       </c>
       <c r="J9" s="1">
         <v>1.84</v>
@@ -1120,10 +1120,10 @@
         <v>36</v>
       </c>
       <c r="H10" s="1">
-        <v>1.708</v>
+        <v>1.82</v>
       </c>
       <c r="I10" s="1">
-        <v>85.40000000000001</v>
+        <v>91</v>
       </c>
       <c r="J10" s="1">
         <v>1.85</v>
@@ -1164,10 +1164,10 @@
         <v>36</v>
       </c>
       <c r="H11" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I11" s="1">
-        <v>103.14</v>
+        <v>109.2</v>
       </c>
       <c r="J11" s="1">
         <v>1.85</v>
@@ -1208,10 +1208,10 @@
         <v>36</v>
       </c>
       <c r="H12" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I12" s="1">
-        <v>110.016</v>
+        <v>116.48</v>
       </c>
       <c r="J12" s="1">
         <v>1.85</v>
@@ -1252,10 +1252,10 @@
         <v>36</v>
       </c>
       <c r="H13" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I13" s="1">
-        <v>116.892</v>
+        <v>123.76</v>
       </c>
       <c r="J13" s="1">
         <v>1.85</v>
@@ -1296,10 +1296,10 @@
         <v>36</v>
       </c>
       <c r="H14" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I14" s="1">
-        <v>60.165</v>
+        <v>63.7</v>
       </c>
       <c r="J14" s="1">
         <v>1.85</v>
@@ -1340,10 +1340,10 @@
         <v>36</v>
       </c>
       <c r="H15" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I15" s="1">
-        <v>81.94499999999999</v>
+        <v>86.759</v>
       </c>
       <c r="J15" s="1">
         <v>1.85</v>
@@ -1384,10 +1384,10 @@
         <v>36</v>
       </c>
       <c r="H16" s="1">
-        <v>1.719</v>
+        <v>1.81</v>
       </c>
       <c r="I16" s="1">
-        <v>98.172</v>
+        <v>103.369</v>
       </c>
       <c r="J16" s="1">
         <v>1.84</v>
@@ -1428,10 +1428,10 @@
         <v>36</v>
       </c>
       <c r="H17" s="1">
-        <v>1.719</v>
+        <v>1.81</v>
       </c>
       <c r="I17" s="1">
-        <v>114.846</v>
+        <v>120.926</v>
       </c>
       <c r="J17" s="1">
         <v>1.84</v>
@@ -1472,10 +1472,10 @@
         <v>36</v>
       </c>
       <c r="H18" s="1">
-        <v>1.719</v>
+        <v>1.81</v>
       </c>
       <c r="I18" s="1">
-        <v>80.965</v>
+        <v>85.251</v>
       </c>
       <c r="J18" s="1">
         <v>1.84</v>
@@ -1516,10 +1516,10 @@
         <v>36</v>
       </c>
       <c r="H19" s="1">
-        <v>1.459</v>
+        <v>1.58</v>
       </c>
       <c r="I19" s="1">
-        <v>53.604</v>
+        <v>58.049</v>
       </c>
       <c r="J19" s="1">
         <v>1.61</v>
@@ -1560,10 +1560,10 @@
         <v>36</v>
       </c>
       <c r="H20" s="1">
-        <v>1.719</v>
+        <v>1.81</v>
       </c>
       <c r="I20" s="1">
-        <v>74.003</v>
+        <v>77.92</v>
       </c>
       <c r="J20" s="1">
         <v>1.84</v>
@@ -1604,10 +1604,10 @@
         <v>36</v>
       </c>
       <c r="H21" s="1">
-        <v>1.719</v>
+        <v>1.81</v>
       </c>
       <c r="I21" s="1">
-        <v>64.548</v>
+        <v>67.965</v>
       </c>
       <c r="J21" s="1">
         <v>1.84</v>
@@ -1648,10 +1648,10 @@
         <v>36</v>
       </c>
       <c r="H22" s="1">
-        <v>1.719</v>
+        <v>1.81</v>
       </c>
       <c r="I22" s="1">
-        <v>96.78</v>
+        <v>101.903</v>
       </c>
       <c r="J22" s="1">
         <v>1.84</v>
@@ -1692,10 +1692,10 @@
         <v>36</v>
       </c>
       <c r="H23" s="1">
-        <v>1.719</v>
+        <v>1.81</v>
       </c>
       <c r="I23" s="1">
-        <v>3.782</v>
+        <v>3.982</v>
       </c>
       <c r="J23" s="1">
         <v>1.84</v>
@@ -1736,10 +1736,10 @@
         <v>36</v>
       </c>
       <c r="H24" s="1">
-        <v>1.719</v>
+        <v>1.81</v>
       </c>
       <c r="I24" s="1">
-        <v>71.167</v>
+        <v>74.934</v>
       </c>
       <c r="J24" s="1">
         <v>1.84</v>
@@ -1798,10 +1798,10 @@
         <v>21</v>
       </c>
       <c r="D29" s="9">
-        <v>1.70452</v>
+        <v>1.80626</v>
       </c>
       <c r="E29" s="7">
-        <v>1713.4</v>
+        <v>1815.68</v>
       </c>
       <c r="F29" s="7">
         <v>1845.83</v>
@@ -1818,10 +1818,10 @@
         <v>2</v>
       </c>
       <c r="D30" s="9">
-        <v>1.44672</v>
+        <v>1.56361</v>
       </c>
       <c r="E30" s="7">
-        <v>90.02</v>
+        <v>97.29000000000001</v>
       </c>
       <c r="F30" s="7">
         <v>99.16</v>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="D31" s="9"/>
       <c r="E31" s="11">
-        <v>1803.42</v>
+        <v>1912.97</v>
       </c>
       <c r="F31" s="11">
         <v>1944.99</v>
